--- a/src/attributions/attributions_ig_traj_486.xlsx
+++ b/src/attributions/attributions_ig_traj_486.xlsx
@@ -2137,10 +2137,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B4" t="n">
-        <v>0.03276350945663225</v>
+        <v>0.09528071438674733</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -2149,25 +2149,25 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.001825522603273789</v>
+        <v>0.0132046382429522</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.01185762622544593</v>
+        <v>-0.04044475401796619</v>
       </c>
       <c r="G4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K4" t="n">
-        <v>0.01058726776101633</v>
+        <v>0.07059350225789794</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -2176,16 +2176,16 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.003833361069794471</v>
+        <v>-0.004403693535813363</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.01254188468495997</v>
+        <v>-0.03279689426238658</v>
       </c>
       <c r="P4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>-0</v>
@@ -2194,115 +2194,115 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>0.001132631627151961</v>
+        <v>-0.02058364082593152</v>
       </c>
       <c r="U4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.001377461757616241</v>
+        <v>-0.02106821525423928</v>
       </c>
       <c r="X4" t="n">
-        <v>1.080034111144805e-11</v>
+        <v>-5.214121831990817e-11</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.01130937159304291</v>
+        <v>-0.04570826313552867</v>
       </c>
       <c r="AD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.02796525786493386</v>
+        <v>-0.05625532860028</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.0004475150030584911</v>
+        <v>-0.05030808583802757</v>
       </c>
       <c r="AH4" t="n">
         <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ4" t="n">
         <v>-0</v>
       </c>
       <c r="AK4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.008065468200349648</v>
+        <v>0.06388590254755837</v>
       </c>
       <c r="AM4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN4" t="n">
         <v>0</v>
       </c>
       <c r="AO4" t="n">
-        <v>-0.0127300218767719</v>
+        <v>-0.0527558870735391</v>
       </c>
       <c r="AP4" t="n">
-        <v>-0.01507168228660197</v>
+        <v>-0.09233783328490294</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS4" t="n">
         <v>0</v>
       </c>
       <c r="AT4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.06812421174559165</v>
+        <v>0.4876244792108886</v>
       </c>
       <c r="AV4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW4" t="n">
         <v>0</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.01239972758328556</v>
+        <v>-0.095946280078405</v>
       </c>
       <c r="AY4" t="n">
-        <v>-0.04766705571176</v>
+        <v>-0.134804435060357</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA4" t="n">
         <v>0</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.02038328183949592</v>
+        <v>-0.01087494137015311</v>
       </c>
       <c r="BE4" t="n">
         <v>0</v>
@@ -2311,160 +2311,160 @@
         <v>0</v>
       </c>
       <c r="BG4" t="n">
-        <v>-0.02543532462227479</v>
+        <v>-0.03253808252702255</v>
       </c>
       <c r="BH4" t="n">
-        <v>-0.01682038694417727</v>
+        <v>-0.05528449492902732</v>
       </c>
       <c r="BI4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.0147648964583839</v>
+        <v>0.05531805097705497</v>
       </c>
       <c r="BN4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO4" t="n">
         <v>-0</v>
       </c>
       <c r="BP4" t="n">
-        <v>-0.004482282374512428</v>
+        <v>0.09749090633071333</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0.01464101173700596</v>
+        <v>0.104470019982319</v>
       </c>
       <c r="BR4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT4" t="n">
         <v>0</v>
       </c>
       <c r="BU4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.02584448840319688</v>
+        <v>0.1202170415278379</v>
       </c>
       <c r="BW4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BX4" t="n">
         <v>0</v>
       </c>
       <c r="BY4" t="n">
-        <v>-0.004997074947352915</v>
+        <v>-0.09209237685303753</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0.00627614339818889</v>
+        <v>-0.1685573517544339</v>
       </c>
       <c r="CA4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB4" t="n">
         <v>0</v>
       </c>
       <c r="CC4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE4" t="n">
-        <v>-0.01492438147419327</v>
+        <v>-0.08980840158959398</v>
       </c>
       <c r="CF4" t="n">
         <v>0</v>
       </c>
       <c r="CG4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CH4" t="n">
-        <v>-0.004200706188711405</v>
+        <v>-0.03619634002697616</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.02726724671057118</v>
+        <v>0.1010674161381174</v>
       </c>
       <c r="CJ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK4" t="n">
         <v>0</v>
       </c>
       <c r="CL4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CN4" t="n">
-        <v>0.004216879112231519</v>
+        <v>-0.0870423901730511</v>
       </c>
       <c r="CO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ4" t="n">
-        <v>0.005173999437150061</v>
+        <v>0.05897734440000277</v>
       </c>
       <c r="CR4" t="n">
-        <v>-0.004557152449952104</v>
+        <v>0.0525881172405257</v>
       </c>
       <c r="CS4" t="n">
         <v>0</v>
       </c>
       <c r="CT4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW4" t="n">
-        <v>-0.01042813076509494</v>
+        <v>-0.08735888290244431</v>
       </c>
       <c r="CX4" t="n">
         <v>0</v>
       </c>
       <c r="CY4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CZ4" t="n">
-        <v>-0.006631342201537867</v>
+        <v>-0.03379891001323557</v>
       </c>
       <c r="DA4" t="n">
-        <v>0.02839556594626354</v>
+        <v>0.09153195363285424</v>
       </c>
       <c r="DB4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF4" t="n">
-        <v>-0.02411695775558477</v>
+        <v>-0.02735806596619373</v>
       </c>
       <c r="DG4" t="n">
         <v>-0</v>
@@ -2473,10 +2473,10 @@
         <v>-0</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.01068165599654949</v>
+        <v>-0.1054241883989323</v>
       </c>
       <c r="DJ4" t="n">
-        <v>0.05824006091708468</v>
+        <v>0.09642847254433658</v>
       </c>
       <c r="DK4" t="n">
         <v>0</v>
@@ -2485,121 +2485,121 @@
         <v>-0</v>
       </c>
       <c r="DM4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN4" t="n">
         <v>-0</v>
       </c>
       <c r="DO4" t="n">
-        <v>-0.007069939536975461</v>
+        <v>-0.03604761667579765</v>
       </c>
       <c r="DP4" t="n">
         <v>0</v>
       </c>
       <c r="DQ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR4" t="n">
-        <v>0.005973507112298083</v>
+        <v>0.04485498744468485</v>
       </c>
       <c r="DS4" t="n">
-        <v>-0.0008932234267189413</v>
+        <v>0.1208159069582155</v>
       </c>
       <c r="DT4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW4" t="n">
         <v>-0</v>
       </c>
       <c r="DX4" t="n">
-        <v>0.002595764798606746</v>
+        <v>0.01999319624178682</v>
       </c>
       <c r="DY4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA4" t="n">
-        <v>-0.007401647323873581</v>
+        <v>-0.002631145508429765</v>
       </c>
       <c r="EB4" t="n">
-        <v>-0.0214110319298971</v>
+        <v>-0.02496242731519139</v>
       </c>
       <c r="EC4" t="n">
         <v>-0</v>
       </c>
       <c r="ED4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG4" t="n">
-        <v>-0.002052184032568215</v>
+        <v>-0.0984116192335073</v>
       </c>
       <c r="EH4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ4" t="n">
-        <v>-0.003259728500040384</v>
+        <v>-0.080970273753962</v>
       </c>
       <c r="EK4" t="n">
-        <v>0.01038335158299949</v>
+        <v>0.04088565754894768</v>
       </c>
       <c r="EL4" t="n">
         <v>-0</v>
       </c>
       <c r="EM4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP4" t="n">
-        <v>-0.00774424024209937</v>
+        <v>-0.01420900411376178</v>
       </c>
       <c r="EQ4" t="n">
         <v>-0</v>
       </c>
       <c r="ER4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES4" t="n">
-        <v>-0.007410270201176714</v>
+        <v>-0.0766463537626013</v>
       </c>
       <c r="ET4" t="n">
-        <v>0.04320249470336338</v>
+        <v>0.1101491121064015</v>
       </c>
       <c r="EU4" t="n">
         <v>0</v>
       </c>
       <c r="EV4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW4" t="n">
         <v>-0</v>
       </c>
       <c r="EX4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY4" t="n">
-        <v>-0.01259366105433556</v>
+        <v>-0.1032309029886891</v>
       </c>
       <c r="EZ4" t="n">
         <v>-0</v>
@@ -2608,25 +2608,25 @@
         <v>0</v>
       </c>
       <c r="FB4" t="n">
-        <v>-0.003858663773374175</v>
+        <v>-0.06140104543285535</v>
       </c>
       <c r="FC4" t="n">
-        <v>0.02826244091206279</v>
+        <v>0.0925171936062644</v>
       </c>
       <c r="FD4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG4" t="n">
         <v>0</v>
       </c>
       <c r="FH4" t="n">
-        <v>-0.01190629744251584</v>
+        <v>-0.09842777787129854</v>
       </c>
       <c r="FI4" t="n">
         <v>0</v>
@@ -2635,10 +2635,10 @@
         <v>-0</v>
       </c>
       <c r="FK4" t="n">
-        <v>-0.01662414476635093</v>
+        <v>-0.02299489781171381</v>
       </c>
       <c r="FL4" t="n">
-        <v>-0.0007817360667597026</v>
+        <v>0.028428681244305</v>
       </c>
       <c r="FM4" t="n">
         <v>0</v>
@@ -2647,40 +2647,40 @@
         <v>-0</v>
       </c>
       <c r="FO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ4" t="n">
-        <v>-0.003262330254398288</v>
+        <v>0.03072647897123151</v>
       </c>
       <c r="FR4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FT4" t="n">
-        <v>-0.01187198918034226</v>
+        <v>0.02590148658064386</v>
       </c>
       <c r="FU4" t="n">
-        <v>0.02537851028209138</v>
+        <v>0.1294026513409484</v>
       </c>
       <c r="FV4" t="n">
         <v>-0</v>
       </c>
       <c r="FW4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ4" t="n">
-        <v>-0.02577397325960054</v>
+        <v>0.001902170721173438</v>
       </c>
       <c r="GA4" t="n">
         <v>0</v>
@@ -2689,10 +2689,10 @@
         <v>-0</v>
       </c>
       <c r="GC4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD4" t="n">
-        <v>-0.007688173775044536</v>
+        <v>0.08767248930444373</v>
       </c>
       <c r="GE4" t="n">
         <v>0</v>
@@ -2701,24 +2701,24 @@
         <v>0</v>
       </c>
       <c r="GG4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B5" t="n">
-        <v>0.1725076330758302</v>
+        <v>0.1283731151583382</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.02180310692589288</v>
+        <v>-0.02488666138761383</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.02729969082365514</v>
+        <v>-0.03200446947023613</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -2727,25 +2727,25 @@
         <v>-0</v>
       </c>
       <c r="H5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K5" t="n">
-        <v>0.06764337411607269</v>
+        <v>0.06996119852617595</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>0.03229706831179462</v>
+        <v>0.05906854076720107</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.02279696653392713</v>
+        <v>-0.02730566121921996</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -2760,22 +2760,22 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T5" t="n">
-        <v>0.03294803469753383</v>
+        <v>0.01892066392769116</v>
       </c>
       <c r="U5" t="n">
         <v>-0</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.01662877420549334</v>
+        <v>-0.003517804099679821</v>
       </c>
       <c r="W5" t="n">
-        <v>0.001233289529426772</v>
+        <v>-3.789807873648358e-05</v>
       </c>
       <c r="X5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
         <v>-0</v>
@@ -2787,25 +2787,25 @@
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.03653994563720792</v>
+        <v>-0.008390375702787198</v>
       </c>
       <c r="AD5" t="n">
         <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.008797751429509835</v>
+        <v>-0.0559405248713423</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.009469049092518559</v>
+        <v>-0.07796501926411188</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
         <v>-0</v>
@@ -2814,73 +2814,73 @@
         <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.06621518157965676</v>
+        <v>0.1029327146228369</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN5" t="n">
-        <v>-0.06667113988620052</v>
+        <v>-0.009688729471383729</v>
       </c>
       <c r="AO5" t="n">
-        <v>-0.07415978904560588</v>
+        <v>0.07425141336767571</v>
       </c>
       <c r="AP5" t="n">
         <v>0</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS5" t="n">
         <v>0</v>
       </c>
       <c r="AT5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.4648498835501819</v>
+        <v>0.306828821162763</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW5" t="n">
-        <v>-0.04625313826043628</v>
+        <v>-0.1467185683320914</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.1212724394851372</v>
+        <v>-0.1103776864891896</v>
       </c>
       <c r="AY5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB5" t="n">
         <v>-0</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD5" t="n">
-        <v>-0.006843307917055892</v>
+        <v>-0.0135865846564232</v>
       </c>
       <c r="BE5" t="n">
         <v>0</v>
       </c>
       <c r="BF5" t="n">
-        <v>-0.03848890279230851</v>
+        <v>-0.0009690913886367163</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0.1120087315799984</v>
+        <v>-0.03572397059984156</v>
       </c>
       <c r="BH5" t="n">
         <v>0</v>
@@ -2895,25 +2895,25 @@
         <v>0</v>
       </c>
       <c r="BL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.06732683903610946</v>
+        <v>-0.02068639408766487</v>
       </c>
       <c r="BN5" t="n">
         <v>-0</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.08785771270982229</v>
+        <v>0.03852870690276527</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.07045361568940724</v>
+        <v>0.07214547566636464</v>
       </c>
       <c r="BQ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS5" t="n">
         <v>-0</v>
@@ -2925,25 +2925,25 @@
         <v>-0</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.1969932709978059</v>
+        <v>0.1636907596364701</v>
       </c>
       <c r="BW5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX5" t="n">
-        <v>-0.03779045920053772</v>
+        <v>-0.09380416001602508</v>
       </c>
       <c r="BY5" t="n">
-        <v>0.01119995587204299</v>
+        <v>0.001608094956242266</v>
       </c>
       <c r="BZ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA5" t="n">
         <v>-0</v>
       </c>
       <c r="CB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC5" t="n">
         <v>0</v>
@@ -2952,43 +2952,43 @@
         <v>-0</v>
       </c>
       <c r="CE5" t="n">
-        <v>-0.08736201735187987</v>
+        <v>-0.1170794855567395</v>
       </c>
       <c r="CF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG5" t="n">
-        <v>0.03877737947138539</v>
+        <v>0.07827728357945164</v>
       </c>
       <c r="CH5" t="n">
-        <v>-0.01675677329128981</v>
+        <v>0.01736302807735395</v>
       </c>
       <c r="CI5" t="n">
         <v>-0</v>
       </c>
       <c r="CJ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK5" t="n">
         <v>0</v>
       </c>
       <c r="CL5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM5" t="n">
         <v>0</v>
       </c>
       <c r="CN5" t="n">
-        <v>0.01692597454174833</v>
+        <v>-0.04098039391308953</v>
       </c>
       <c r="CO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP5" t="n">
-        <v>-0.007107240512562601</v>
+        <v>0.01125914365373463</v>
       </c>
       <c r="CQ5" t="n">
-        <v>-0.05956465918013554</v>
+        <v>0.00768575898157436</v>
       </c>
       <c r="CR5" t="n">
         <v>0</v>
@@ -3000,22 +3000,22 @@
         <v>-0</v>
       </c>
       <c r="CU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW5" t="n">
-        <v>-0.07648767343688373</v>
+        <v>-0.1251983260787105</v>
       </c>
       <c r="CX5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY5" t="n">
-        <v>0.0540964021793269</v>
+        <v>0.08834480148794106</v>
       </c>
       <c r="CZ5" t="n">
-        <v>-0.009676900314524565</v>
+        <v>0.02525910054900036</v>
       </c>
       <c r="DA5" t="n">
         <v>0</v>
@@ -3027,31 +3027,31 @@
         <v>0</v>
       </c>
       <c r="DD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE5" t="n">
         <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>-0.002559057853337056</v>
+        <v>-0.00561835382350237</v>
       </c>
       <c r="DG5" t="n">
         <v>0</v>
       </c>
       <c r="DH5" t="n">
-        <v>0.0311545474589653</v>
+        <v>0.03545477439815864</v>
       </c>
       <c r="DI5" t="n">
-        <v>-0.04007543775209302</v>
+        <v>-0.06449925329717986</v>
       </c>
       <c r="DJ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM5" t="n">
         <v>0</v>
@@ -3060,52 +3060,52 @@
         <v>-0</v>
       </c>
       <c r="DO5" t="n">
-        <v>-0.09983195477489447</v>
+        <v>-0.07134175415904437</v>
       </c>
       <c r="DP5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DQ5" t="n">
-        <v>0.01115872141999645</v>
+        <v>0.03399645209405225</v>
       </c>
       <c r="DR5" t="n">
-        <v>-0.03011842749577147</v>
+        <v>-0.05179931529392985</v>
       </c>
       <c r="DS5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT5" t="n">
         <v>-0</v>
       </c>
       <c r="DU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV5" t="n">
         <v>0</v>
       </c>
       <c r="DW5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX5" t="n">
-        <v>-0.007351348611382303</v>
+        <v>0.06745890302743493</v>
       </c>
       <c r="DY5" t="n">
         <v>0</v>
       </c>
       <c r="DZ5" t="n">
-        <v>-0.01965632256800486</v>
+        <v>0.06529641745680076</v>
       </c>
       <c r="EA5" t="n">
-        <v>-0.02250586269243579</v>
+        <v>-0.06126547347944625</v>
       </c>
       <c r="EB5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC5" t="n">
         <v>0</v>
       </c>
       <c r="ED5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE5" t="n">
         <v>-0</v>
@@ -3114,97 +3114,97 @@
         <v>0</v>
       </c>
       <c r="EG5" t="n">
-        <v>-0.05415452493264417</v>
+        <v>-0.06012237850875879</v>
       </c>
       <c r="EH5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI5" t="n">
-        <v>0.02969823739104683</v>
+        <v>0.08635043321050605</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0.03880809722909598</v>
+        <v>0.02130355781995271</v>
       </c>
       <c r="EK5" t="n">
         <v>-0</v>
       </c>
       <c r="EL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM5" t="n">
         <v>-0</v>
       </c>
       <c r="EN5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO5" t="n">
         <v>0</v>
       </c>
       <c r="EP5" t="n">
-        <v>-0.06573723954100572</v>
+        <v>-0.07838814139224219</v>
       </c>
       <c r="EQ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER5" t="n">
-        <v>0.06567924385171252</v>
+        <v>0.06932969504846766</v>
       </c>
       <c r="ES5" t="n">
-        <v>-0.05110407726070637</v>
+        <v>-0.04266630045419986</v>
       </c>
       <c r="ET5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW5" t="n">
         <v>-0</v>
       </c>
       <c r="EX5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY5" t="n">
-        <v>-0.08307545331796262</v>
+        <v>-0.1334172141736419</v>
       </c>
       <c r="EZ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA5" t="n">
-        <v>0.05792915837632899</v>
+        <v>0.09986447957221929</v>
       </c>
       <c r="FB5" t="n">
-        <v>-0.02184914540443966</v>
+        <v>0.006576339709837654</v>
       </c>
       <c r="FC5" t="n">
         <v>-0</v>
       </c>
       <c r="FD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH5" t="n">
-        <v>-0.0008255452366848725</v>
+        <v>-0.04560568267486861</v>
       </c>
       <c r="FI5" t="n">
         <v>-0</v>
       </c>
       <c r="FJ5" t="n">
-        <v>-0.05322965409877631</v>
+        <v>0.001379782756052381</v>
       </c>
       <c r="FK5" t="n">
-        <v>0.01272188604132879</v>
+        <v>0.03792191498365648</v>
       </c>
       <c r="FL5" t="n">
         <v>-0</v>
@@ -3216,25 +3216,25 @@
         <v>-0</v>
       </c>
       <c r="FO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ5" t="n">
-        <v>-0.01922731356918217</v>
+        <v>0.00954456206744219</v>
       </c>
       <c r="FR5" t="n">
         <v>-0</v>
       </c>
       <c r="FS5" t="n">
-        <v>0.06604055044422193</v>
+        <v>0.169937627305312</v>
       </c>
       <c r="FT5" t="n">
-        <v>0.06031951217221503</v>
+        <v>-0.06109497161789108</v>
       </c>
       <c r="FU5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV5" t="n">
         <v>-0</v>
@@ -3246,28 +3246,28 @@
         <v>0</v>
       </c>
       <c r="FY5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ5" t="n">
-        <v>-0.0360580900356367</v>
+        <v>-0.08158355318821475</v>
       </c>
       <c r="GA5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB5" t="n">
-        <v>0.03573982829320457</v>
+        <v>0.03591809410647144</v>
       </c>
       <c r="GC5" t="n">
         <v>0</v>
       </c>
       <c r="GD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE5" t="n">
         <v>-0</v>
       </c>
       <c r="GF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG5" t="n">
         <v>-0</v>
@@ -3275,10 +3275,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B6" t="n">
-        <v>0.01399830006829453</v>
+        <v>0.03225038926238935</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -3287,25 +3287,25 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.001490698288288336</v>
+        <v>0.01480866900691414</v>
       </c>
       <c r="F6" t="n">
-        <v>0.001585941674975023</v>
+        <v>0.005401604900543618</v>
       </c>
       <c r="G6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0.005078656876929392</v>
+        <v>0.03920280237553151</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -3314,16 +3314,16 @@
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.003381607136297269</v>
+        <v>0.005718618382582289</v>
       </c>
       <c r="O6" t="n">
-        <v>0.001412934775920501</v>
+        <v>0.003276566947969452</v>
       </c>
       <c r="P6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -3332,7 +3332,7 @@
         <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0002845499326110335</v>
+        <v>-0.009615541890389495</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -3341,43 +3341,43 @@
         <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.001748775871148526</v>
+        <v>-0.01261030381188768</v>
       </c>
       <c r="X6" t="n">
-        <v>5.060823521058788e-12</v>
+        <v>-2.001848620866948e-12</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z6" t="n">
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB6" t="n">
         <v>-0</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.01256946170422866</v>
+        <v>-0.0237847593818904</v>
       </c>
       <c r="AD6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.01321442655674176</v>
+        <v>-0.05903200246762668</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.002147300223689504</v>
+        <v>-0.02670936681813369</v>
       </c>
       <c r="AH6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ6" t="n">
         <v>-0</v>
@@ -3386,22 +3386,22 @@
         <v>0</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.004911402981420735</v>
+        <v>0.004306308244201403</v>
       </c>
       <c r="AM6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN6" t="n">
         <v>0</v>
       </c>
       <c r="AO6" t="n">
-        <v>-0.01321511146824106</v>
+        <v>-0.01749255961275626</v>
       </c>
       <c r="AP6" t="n">
-        <v>-0.006121756138462169</v>
+        <v>-0.0471797756967574</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR6" t="n">
         <v>0</v>
@@ -3410,10 +3410,10 @@
         <v>0</v>
       </c>
       <c r="AT6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.04225976884282072</v>
+        <v>0.1503565843019433</v>
       </c>
       <c r="AV6" t="n">
         <v>0</v>
@@ -3422,10 +3422,10 @@
         <v>0</v>
       </c>
       <c r="AX6" t="n">
-        <v>0.001491774350914703</v>
+        <v>-0.03195503968620989</v>
       </c>
       <c r="AY6" t="n">
-        <v>-0.008574242950358918</v>
+        <v>-0.03339576900123909</v>
       </c>
       <c r="AZ6" t="n">
         <v>0</v>
@@ -3437,10 +3437,10 @@
         <v>-0</v>
       </c>
       <c r="BC6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.003416564253152589</v>
+        <v>-0.01274511136519259</v>
       </c>
       <c r="BE6" t="n">
         <v>0</v>
@@ -3449,25 +3449,25 @@
         <v>0</v>
       </c>
       <c r="BG6" t="n">
-        <v>-0.01151183167652253</v>
+        <v>-0.01441832839348547</v>
       </c>
       <c r="BH6" t="n">
-        <v>-0.001619682603901777</v>
+        <v>-0.008463723725144029</v>
       </c>
       <c r="BI6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK6" t="n">
         <v>0</v>
       </c>
       <c r="BL6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.01538785064575639</v>
+        <v>0.03252321435486985</v>
       </c>
       <c r="BN6" t="n">
         <v>0</v>
@@ -3476,25 +3476,25 @@
         <v>-0</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.009939228415054964</v>
+        <v>0.06055979903469982</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0.009753670634919276</v>
+        <v>0.04651978735385965</v>
       </c>
       <c r="BR6" t="n">
         <v>-0</v>
       </c>
       <c r="BS6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BU6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.008448895233777709</v>
+        <v>0.03200254065259876</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
@@ -3503,13 +3503,13 @@
         <v>0</v>
       </c>
       <c r="BY6" t="n">
-        <v>-0.004474831394699949</v>
+        <v>-0.008474270948720865</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0.01117053541197531</v>
+        <v>-0.0417404230378927</v>
       </c>
       <c r="CA6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB6" t="n">
         <v>0</v>
@@ -3521,7 +3521,7 @@
         <v>-0</v>
       </c>
       <c r="CE6" t="n">
-        <v>-0.001888068119507478</v>
+        <v>-0.01733764677720248</v>
       </c>
       <c r="CF6" t="n">
         <v>-0</v>
@@ -3530,13 +3530,13 @@
         <v>0</v>
       </c>
       <c r="CH6" t="n">
-        <v>-0.0009086560581374654</v>
+        <v>-0.0006287228150216573</v>
       </c>
       <c r="CI6" t="n">
-        <v>0.005237184008743086</v>
+        <v>0.03168714321486692</v>
       </c>
       <c r="CJ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK6" t="n">
         <v>0</v>
@@ -3548,73 +3548,73 @@
         <v>0</v>
       </c>
       <c r="CN6" t="n">
-        <v>0.003350987349969835</v>
+        <v>-0.01644602357079398</v>
       </c>
       <c r="CO6" t="n">
         <v>-0</v>
       </c>
       <c r="CP6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CQ6" t="n">
-        <v>0.00239968101026783</v>
+        <v>0.03384067439023204</v>
       </c>
       <c r="CR6" t="n">
-        <v>-0.008216524446693298</v>
+        <v>0.02168195205085565</v>
       </c>
       <c r="CS6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW6" t="n">
-        <v>0.0009363635232834875</v>
+        <v>-0.01963720078456203</v>
       </c>
       <c r="CX6" t="n">
         <v>0</v>
       </c>
       <c r="CY6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CZ6" t="n">
-        <v>-0.0005558238925389629</v>
+        <v>-0.005911446183413402</v>
       </c>
       <c r="DA6" t="n">
-        <v>0.007153011530116884</v>
+        <v>0.02665469572094194</v>
       </c>
       <c r="DB6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD6" t="n">
         <v>0</v>
       </c>
       <c r="DE6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF6" t="n">
-        <v>-0.004331410657890332</v>
+        <v>0.003796960667528582</v>
       </c>
       <c r="DG6" t="n">
         <v>-0</v>
       </c>
       <c r="DH6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.0001820347106107003</v>
+        <v>-0.001272357585903274</v>
       </c>
       <c r="DJ6" t="n">
-        <v>0.01078147676059298</v>
+        <v>0.002665686345460856</v>
       </c>
       <c r="DK6" t="n">
         <v>0</v>
@@ -3623,25 +3623,25 @@
         <v>-0</v>
       </c>
       <c r="DM6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN6" t="n">
         <v>-0</v>
       </c>
       <c r="DO6" t="n">
-        <v>0.005425967600219902</v>
+        <v>-0.004724759002170616</v>
       </c>
       <c r="DP6" t="n">
         <v>-0</v>
       </c>
       <c r="DQ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR6" t="n">
-        <v>0.01139496699511015</v>
+        <v>-0.006466709943555874</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.002830939344923979</v>
+        <v>0.04622112589764295</v>
       </c>
       <c r="DT6" t="n">
         <v>-0</v>
@@ -3656,46 +3656,46 @@
         <v>-0</v>
       </c>
       <c r="DX6" t="n">
-        <v>-0.007956887177382931</v>
+        <v>0.008822598029739418</v>
       </c>
       <c r="DY6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA6" t="n">
-        <v>-0.00609393969531359</v>
+        <v>-0.02863233443540659</v>
       </c>
       <c r="EB6" t="n">
-        <v>-0.004515128753220258</v>
+        <v>0.01248219068711015</v>
       </c>
       <c r="EC6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE6" t="n">
         <v>-0</v>
       </c>
       <c r="EF6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG6" t="n">
-        <v>-0.001624080092189488</v>
+        <v>-0.013702304480783</v>
       </c>
       <c r="EH6" t="n">
         <v>-0</v>
       </c>
       <c r="EI6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ6" t="n">
-        <v>0.0008879189737606125</v>
+        <v>-0.01749679010575112</v>
       </c>
       <c r="EK6" t="n">
-        <v>0.006741673978075875</v>
+        <v>-0.004396888070529813</v>
       </c>
       <c r="EL6" t="n">
         <v>-0</v>
@@ -3707,76 +3707,76 @@
         <v>-0</v>
       </c>
       <c r="EO6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP6" t="n">
-        <v>-0.002679100115464995</v>
+        <v>-0.003515864196809364</v>
       </c>
       <c r="EQ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ES6" t="n">
-        <v>-0.009466616542981955</v>
+        <v>-0.02323010987060278</v>
       </c>
       <c r="ET6" t="n">
-        <v>0.02862456637400686</v>
+        <v>0.03854292558184182</v>
       </c>
       <c r="EU6" t="n">
         <v>0</v>
       </c>
       <c r="EV6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY6" t="n">
-        <v>0.003111415510248673</v>
+        <v>-0.02513227173192471</v>
       </c>
       <c r="EZ6" t="n">
         <v>-0</v>
       </c>
       <c r="FA6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FB6" t="n">
-        <v>-0.001742168813322883</v>
+        <v>-0.013408566248388</v>
       </c>
       <c r="FC6" t="n">
-        <v>0.007825350710120943</v>
+        <v>0.02204892515440451</v>
       </c>
       <c r="FD6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF6" t="n">
         <v>-0</v>
       </c>
       <c r="FG6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH6" t="n">
-        <v>-0.007876149008094501</v>
+        <v>-0.01717583445637263</v>
       </c>
       <c r="FI6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FK6" t="n">
-        <v>-0.01474197624828361</v>
+        <v>0.009735014480703305</v>
       </c>
       <c r="FL6" t="n">
-        <v>0.01929041678151275</v>
+        <v>-0.004240755898128984</v>
       </c>
       <c r="FM6" t="n">
         <v>0</v>
@@ -3785,13 +3785,13 @@
         <v>-0</v>
       </c>
       <c r="FO6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ6" t="n">
-        <v>-0.003670851183439456</v>
+        <v>0.0440840736714301</v>
       </c>
       <c r="FR6" t="n">
         <v>-0</v>
@@ -3800,10 +3800,10 @@
         <v>-0</v>
       </c>
       <c r="FT6" t="n">
-        <v>0.00175517936337977</v>
+        <v>0.004206973694631078</v>
       </c>
       <c r="FU6" t="n">
-        <v>6.014402195769862e-05</v>
+        <v>-0.03099206789207634</v>
       </c>
       <c r="FV6" t="n">
         <v>-0</v>
@@ -3815,22 +3815,22 @@
         <v>-0</v>
       </c>
       <c r="FY6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ6" t="n">
-        <v>-0.0145298205951637</v>
+        <v>0.01388990464984758</v>
       </c>
       <c r="GA6" t="n">
         <v>0</v>
       </c>
       <c r="GB6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC6" t="n">
         <v>-0</v>
       </c>
       <c r="GD6" t="n">
-        <v>-0.001006405095225285</v>
+        <v>0.01172021955402397</v>
       </c>
       <c r="GE6" t="n">
         <v>0</v>
@@ -3847,7 +3847,7 @@
         <v>0</v>
       </c>
       <c r="B7" t="n">
-        <v>0.07960306541686911</v>
+        <v>0.05115968743009374</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -3856,34 +3856,34 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.007684258176630763</v>
+        <v>-0.01855907868252326</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
         <v>-0</v>
       </c>
       <c r="I7" t="n">
-        <v>0.009727471023391528</v>
+        <v>0.004798381239547209</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.03298108849715247</v>
+        <v>0.05984583834315271</v>
       </c>
       <c r="L7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.03197815436808706</v>
+        <v>-0.01632725962752507</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -3892,16 +3892,16 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.007549183742255119</v>
+        <v>0.001323968123323138</v>
       </c>
       <c r="S7" t="n">
         <v>-0</v>
       </c>
       <c r="T7" t="n">
-        <v>0.01010536207092292</v>
+        <v>-0.008190621891701243</v>
       </c>
       <c r="U7" t="n">
         <v>-0</v>
@@ -3910,34 +3910,34 @@
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.003796336482824871</v>
+        <v>-0.02066484806860732</v>
       </c>
       <c r="X7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA7" t="n">
-        <v>-9.088522102059491e-13</v>
+        <v>-7.65149895482211e-13</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.03343396184074643</v>
+        <v>-0.03207951675909655</v>
       </c>
       <c r="AD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.03271864116948899</v>
+        <v>-0.03208028706246078</v>
       </c>
       <c r="AG7" t="n">
         <v>0</v>
@@ -3946,16 +3946,16 @@
         <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.01772989980438029</v>
+        <v>-0.000264338111070469</v>
       </c>
       <c r="AK7" t="n">
         <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.03151736937986847</v>
+        <v>0.0314044332476583</v>
       </c>
       <c r="AM7" t="n">
         <v>0</v>
@@ -3964,37 +3964,37 @@
         <v>0</v>
       </c>
       <c r="AO7" t="n">
-        <v>-0.02491453501993047</v>
+        <v>-0.01302193300615565</v>
       </c>
       <c r="AP7" t="n">
         <v>0</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR7" t="n">
         <v>0</v>
       </c>
       <c r="AS7" t="n">
-        <v>-0.02089777370143433</v>
+        <v>-0.01994714801349232</v>
       </c>
       <c r="AT7" t="n">
         <v>-0</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.2080069058601355</v>
+        <v>0.1414574595492603</v>
       </c>
       <c r="AV7" t="n">
         <v>-0</v>
       </c>
       <c r="AW7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.09581812752758578</v>
+        <v>-0.02661363893532226</v>
       </c>
       <c r="AY7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AZ7" t="n">
         <v>0</v>
@@ -4003,94 +4003,94 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>-0.0009988295270125867</v>
+        <v>0.01415967513632339</v>
       </c>
       <c r="BC7" t="n">
         <v>0</v>
       </c>
       <c r="BD7" t="n">
-        <v>-0.0124436398940785</v>
+        <v>-0.00870870714833428</v>
       </c>
       <c r="BE7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BF7" t="n">
         <v>0</v>
       </c>
       <c r="BG7" t="n">
-        <v>-0.06434634007978753</v>
+        <v>-0.02689690800761656</v>
       </c>
       <c r="BH7" t="n">
         <v>0</v>
       </c>
       <c r="BI7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK7" t="n">
-        <v>-0.004683698006418705</v>
+        <v>-0.003921151740072974</v>
       </c>
       <c r="BL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.00103304185125799</v>
+        <v>0.02206313476818171</v>
       </c>
       <c r="BN7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.08494146350797682</v>
+        <v>0.0475649993437277</v>
       </c>
       <c r="BQ7" t="n">
         <v>-0</v>
       </c>
       <c r="BR7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS7" t="n">
         <v>-0</v>
       </c>
       <c r="BT7" t="n">
-        <v>0.03815127279809411</v>
+        <v>0.02101559122440947</v>
       </c>
       <c r="BU7" t="n">
         <v>-0</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.07616695707333027</v>
+        <v>0.05678510677819534</v>
       </c>
       <c r="BW7" t="n">
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.01807387093277464</v>
+        <v>-0.02262307914644784</v>
       </c>
       <c r="BZ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB7" t="n">
         <v>0</v>
       </c>
       <c r="CC7" t="n">
-        <v>0.00887244393693856</v>
+        <v>-0.01715818100884693</v>
       </c>
       <c r="CD7" t="n">
         <v>-0</v>
       </c>
       <c r="CE7" t="n">
-        <v>-0.02480422431924459</v>
+        <v>-0.0293339943105438</v>
       </c>
       <c r="CF7" t="n">
         <v>-0</v>
@@ -4099,10 +4099,10 @@
         <v>-0</v>
       </c>
       <c r="CH7" t="n">
-        <v>-0.004069030771666751</v>
+        <v>0.007503343274785157</v>
       </c>
       <c r="CI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ7" t="n">
         <v>-0</v>
@@ -4111,25 +4111,25 @@
         <v>0</v>
       </c>
       <c r="CL7" t="n">
-        <v>0.02667110136270809</v>
+        <v>0.01690183450141573</v>
       </c>
       <c r="CM7" t="n">
         <v>0</v>
       </c>
       <c r="CN7" t="n">
-        <v>-0.006751033570374652</v>
+        <v>-0.02254147540075025</v>
       </c>
       <c r="CO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ7" t="n">
-        <v>-0.01483268719472366</v>
+        <v>0.004676974388647849</v>
       </c>
       <c r="CR7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS7" t="n">
         <v>-0</v>
@@ -4138,13 +4138,13 @@
         <v>-0</v>
       </c>
       <c r="CU7" t="n">
-        <v>-0.005129424594388519</v>
+        <v>0.01814388763581109</v>
       </c>
       <c r="CV7" t="n">
         <v>0</v>
       </c>
       <c r="CW7" t="n">
-        <v>-0.02226623318530417</v>
+        <v>-0.03108524886601927</v>
       </c>
       <c r="CX7" t="n">
         <v>0</v>
@@ -4153,133 +4153,133 @@
         <v>0</v>
       </c>
       <c r="CZ7" t="n">
-        <v>0.005339862969800489</v>
+        <v>0.003658371343311001</v>
       </c>
       <c r="DA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB7" t="n">
         <v>0</v>
       </c>
       <c r="DC7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD7" t="n">
-        <v>0.02613020316003274</v>
+        <v>0.0154594261999628</v>
       </c>
       <c r="DE7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>-0.08480627395885093</v>
+        <v>-0.0158653107224528</v>
       </c>
       <c r="DG7" t="n">
         <v>-0</v>
       </c>
       <c r="DH7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.02546356756939944</v>
+        <v>-0.006763099486940951</v>
       </c>
       <c r="DJ7" t="n">
         <v>-0</v>
       </c>
       <c r="DK7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM7" t="n">
-        <v>-0.004551196311933782</v>
+        <v>-0.01192604243056283</v>
       </c>
       <c r="DN7" t="n">
         <v>-0</v>
       </c>
       <c r="DO7" t="n">
-        <v>-0.01366687772349984</v>
+        <v>-0.02205423635862449</v>
       </c>
       <c r="DP7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DQ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR7" t="n">
-        <v>-0.00741707412477521</v>
+        <v>0.01504922203812529</v>
       </c>
       <c r="DS7" t="n">
         <v>-0</v>
       </c>
       <c r="DT7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU7" t="n">
         <v>-0</v>
       </c>
       <c r="DV7" t="n">
-        <v>-0.005037128185208509</v>
+        <v>-0.03534162133816138</v>
       </c>
       <c r="DW7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX7" t="n">
-        <v>-0.01184895446828579</v>
+        <v>0.01034744684122034</v>
       </c>
       <c r="DY7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA7" t="n">
-        <v>-0.01009129646812139</v>
+        <v>-0.01042969719026555</v>
       </c>
       <c r="EB7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC7" t="n">
         <v>-0</v>
       </c>
       <c r="ED7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE7" t="n">
-        <v>-0.009181322712941004</v>
+        <v>0.01011968542456711</v>
       </c>
       <c r="EF7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG7" t="n">
-        <v>-0.0007125726661700885</v>
+        <v>-0.02413448353442436</v>
       </c>
       <c r="EH7" t="n">
         <v>0</v>
       </c>
       <c r="EI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ7" t="n">
-        <v>0.03310584038326968</v>
+        <v>-0.005579856731699129</v>
       </c>
       <c r="EK7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM7" t="n">
         <v>0</v>
       </c>
       <c r="EN7" t="n">
-        <v>0.03175999257473078</v>
+        <v>0.008626770975215093</v>
       </c>
       <c r="EO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP7" t="n">
-        <v>-0.04922620189926075</v>
+        <v>-0.003089754754013824</v>
       </c>
       <c r="EQ7" t="n">
         <v>-0</v>
@@ -4288,25 +4288,25 @@
         <v>-0</v>
       </c>
       <c r="ES7" t="n">
-        <v>-0.01009938431152753</v>
+        <v>-0.007905215863267315</v>
       </c>
       <c r="ET7" t="n">
         <v>-0</v>
       </c>
       <c r="EU7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW7" t="n">
-        <v>0.006801322799984487</v>
+        <v>0.01167103960149628</v>
       </c>
       <c r="EX7" t="n">
         <v>-0</v>
       </c>
       <c r="EY7" t="n">
-        <v>-0.03327140285855892</v>
+        <v>-0.03512906641655535</v>
       </c>
       <c r="EZ7" t="n">
         <v>-0</v>
@@ -4315,7 +4315,7 @@
         <v>-0</v>
       </c>
       <c r="FB7" t="n">
-        <v>0.003291073760924235</v>
+        <v>-0.002323016938528354</v>
       </c>
       <c r="FC7" t="n">
         <v>-0</v>
@@ -4327,22 +4327,22 @@
         <v>0</v>
       </c>
       <c r="FF7" t="n">
-        <v>0.01526962131004073</v>
+        <v>0.01609601634001842</v>
       </c>
       <c r="FG7" t="n">
         <v>0</v>
       </c>
       <c r="FH7" t="n">
-        <v>-0.02930865913359087</v>
+        <v>-0.02423730698188837</v>
       </c>
       <c r="FI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FJ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FK7" t="n">
-        <v>-0.01884722259310486</v>
+        <v>-0.000536547410685937</v>
       </c>
       <c r="FL7" t="n">
         <v>0</v>
@@ -4351,16 +4351,16 @@
         <v>0</v>
       </c>
       <c r="FN7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO7" t="n">
-        <v>0.01234517262400897</v>
+        <v>0.0696369257438105</v>
       </c>
       <c r="FP7" t="n">
         <v>-0</v>
       </c>
       <c r="FQ7" t="n">
-        <v>-0.04997103022490521</v>
+        <v>0.0192033203412986</v>
       </c>
       <c r="FR7" t="n">
         <v>-0</v>
@@ -4369,7 +4369,7 @@
         <v>-0</v>
       </c>
       <c r="FT7" t="n">
-        <v>0.0203774922007664</v>
+        <v>-0.01760122010121101</v>
       </c>
       <c r="FU7" t="n">
         <v>-0</v>
@@ -4378,19 +4378,19 @@
         <v>-0</v>
       </c>
       <c r="FW7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX7" t="n">
-        <v>-6.470504767008516e-05</v>
+        <v>0.002151820689947458</v>
       </c>
       <c r="FY7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ7" t="n">
-        <v>-0.04626428153025168</v>
+        <v>-0.00673277386339723</v>
       </c>
       <c r="GA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB7" t="n">
         <v>-0</v>
@@ -4399,16 +4399,16 @@
         <v>0</v>
       </c>
       <c r="GD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG7" t="n">
-        <v>0.03273530586034665</v>
+        <v>0.003655107132254003</v>
       </c>
     </row>
     <row r="8">
@@ -4985,16 +4985,16 @@
         <v>0</v>
       </c>
       <c r="B9" t="n">
-        <v>0.4731684009159721</v>
+        <v>0.1293798955409936</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.1458122041077164</v>
+        <v>-0.1088035881281145</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.03103240815289695</v>
+        <v>-0.05395953028505523</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -5006,22 +5006,22 @@
         <v>-0</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2586849355656163</v>
+        <v>0.1000137174562022</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.09086915207892303</v>
+        <v>-0.102509716557899</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.06662552271210206</v>
+        <v>-0.06408301996370272</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -5033,31 +5033,31 @@
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T9" t="n">
-        <v>0.09239357446080913</v>
+        <v>0.04763530502480835</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.05940438455705745</v>
+        <v>-0.001848898619781162</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.0449670071162726</v>
+        <v>-0.02999576420719311</v>
       </c>
       <c r="X9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
         <v>-0</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -5066,22 +5066,22 @@
         <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.1637130606336009</v>
+        <v>0.04716058962604697</v>
       </c>
       <c r="AD9" t="n">
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>-0.04666321906002877</v>
+        <v>-0.07994175125509598</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.04975911520310321</v>
+        <v>-0.0855710100227907</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
         <v>-0</v>
@@ -5090,25 +5090,25 @@
         <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.1007546610322377</v>
+        <v>0.1293685779559409</v>
       </c>
       <c r="AM9" t="n">
         <v>0</v>
       </c>
       <c r="AN9" t="n">
-        <v>-0.08731947227528171</v>
+        <v>-0.07467472452037852</v>
       </c>
       <c r="AO9" t="n">
-        <v>-0.1228815656978141</v>
+        <v>0.09990334555071113</v>
       </c>
       <c r="AP9" t="n">
         <v>0</v>
       </c>
       <c r="AQ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR9" t="n">
         <v>-0</v>
@@ -5120,43 +5120,43 @@
         <v>-0</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.7521608219460187</v>
+        <v>0.2377613282723405</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW9" t="n">
-        <v>-0.06564491971166547</v>
+        <v>-0.1515618125144429</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.1931316261224824</v>
+        <v>-0.285265582300456</v>
       </c>
       <c r="AY9" t="n">
         <v>-0</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC9" t="n">
         <v>0</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.06047739967661232</v>
+        <v>-0.03961451994162116</v>
       </c>
       <c r="BE9" t="n">
         <v>0</v>
       </c>
       <c r="BF9" t="n">
-        <v>-0.06357286469238957</v>
+        <v>-0.0110492224547295</v>
       </c>
       <c r="BG9" t="n">
-        <v>-0.2335724325762981</v>
+        <v>-0.002260725049187188</v>
       </c>
       <c r="BH9" t="n">
         <v>0</v>
@@ -5165,7 +5165,7 @@
         <v>-0</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK9" t="n">
         <v>0</v>
@@ -5174,22 +5174,22 @@
         <v>-0</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.1361284868284103</v>
+        <v>0.0326533449109129</v>
       </c>
       <c r="BN9" t="n">
         <v>-0</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.0624705118708181</v>
+        <v>0.0290726633623054</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.1213876505452223</v>
+        <v>-0.002957309702652741</v>
       </c>
       <c r="BQ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS9" t="n">
         <v>-0</v>
@@ -5201,19 +5201,19 @@
         <v>-0</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.3053489970240526</v>
+        <v>0.164699740662476</v>
       </c>
       <c r="BW9" t="n">
         <v>0</v>
       </c>
       <c r="BX9" t="n">
-        <v>-0.08413143485834468</v>
+        <v>-0.1473063214691694</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.00949745775143316</v>
+        <v>-0.0576412605270964</v>
       </c>
       <c r="BZ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA9" t="n">
         <v>-0</v>
@@ -5228,22 +5228,22 @@
         <v>-0</v>
       </c>
       <c r="CE9" t="n">
-        <v>-0.1679553545925939</v>
+        <v>-0.0713544695643407</v>
       </c>
       <c r="CF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.03184958288907125</v>
+        <v>0.1396644182616761</v>
       </c>
       <c r="CH9" t="n">
-        <v>-0.0402833679447372</v>
+        <v>0.02447896450498939</v>
       </c>
       <c r="CI9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CJ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK9" t="n">
         <v>0</v>
@@ -5255,16 +5255,16 @@
         <v>0</v>
       </c>
       <c r="CN9" t="n">
-        <v>-0.005299919928234257</v>
+        <v>-0.04879926416013193</v>
       </c>
       <c r="CO9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP9" t="n">
-        <v>-0.08496725489660027</v>
+        <v>0.1165635677578251</v>
       </c>
       <c r="CQ9" t="n">
-        <v>-0.05801578858665819</v>
+        <v>0.05045442676161775</v>
       </c>
       <c r="CR9" t="n">
         <v>0</v>
@@ -5273,31 +5273,31 @@
         <v>-0</v>
       </c>
       <c r="CT9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV9" t="n">
         <v>0</v>
       </c>
       <c r="CW9" t="n">
-        <v>-0.1380279762678077</v>
+        <v>-0.06411493546049384</v>
       </c>
       <c r="CX9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY9" t="n">
-        <v>0.07380173785150601</v>
+        <v>0.1518368045964097</v>
       </c>
       <c r="CZ9" t="n">
-        <v>-0.01724949313481587</v>
+        <v>0.04377457893587494</v>
       </c>
       <c r="DA9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DB9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC9" t="n">
         <v>-0</v>
@@ -5309,49 +5309,49 @@
         <v>0</v>
       </c>
       <c r="DF9" t="n">
-        <v>-0.02693058378240799</v>
+        <v>-0.00217498940724151</v>
       </c>
       <c r="DG9" t="n">
         <v>0</v>
       </c>
       <c r="DH9" t="n">
-        <v>0.1005670093842168</v>
+        <v>0.0629139720567458</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.02815007944276051</v>
+        <v>-0.03437567163072313</v>
       </c>
       <c r="DJ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK9" t="n">
         <v>-0</v>
       </c>
       <c r="DL9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN9" t="n">
         <v>-0</v>
       </c>
       <c r="DO9" t="n">
-        <v>-0.1019704099562367</v>
+        <v>-0.08326247876160069</v>
       </c>
       <c r="DP9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ9" t="n">
-        <v>0.03952710567491419</v>
+        <v>0.1128418384148613</v>
       </c>
       <c r="DR9" t="n">
-        <v>-0.06280255270463987</v>
+        <v>-0.005671696752026479</v>
       </c>
       <c r="DS9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU9" t="n">
         <v>-0</v>
@@ -5360,28 +5360,28 @@
         <v>0</v>
       </c>
       <c r="DW9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX9" t="n">
-        <v>-0.0210922777457749</v>
+        <v>0.04286686499144976</v>
       </c>
       <c r="DY9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ9" t="n">
-        <v>-0.02556410995043632</v>
+        <v>0.07467150690990082</v>
       </c>
       <c r="EA9" t="n">
-        <v>-0.03553069982524062</v>
+        <v>-0.06196764788140146</v>
       </c>
       <c r="EB9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE9" t="n">
         <v>-0</v>
@@ -5390,49 +5390,49 @@
         <v>0</v>
       </c>
       <c r="EG9" t="n">
-        <v>-0.0574944918942888</v>
+        <v>0.02776170382530594</v>
       </c>
       <c r="EH9" t="n">
         <v>0</v>
       </c>
       <c r="EI9" t="n">
-        <v>0.01879142100619051</v>
+        <v>0.1018240124738304</v>
       </c>
       <c r="EJ9" t="n">
-        <v>0.039736433312528</v>
+        <v>0.03656056090512336</v>
       </c>
       <c r="EK9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO9" t="n">
         <v>0</v>
       </c>
       <c r="EP9" t="n">
-        <v>-0.1632279531751215</v>
+        <v>-0.0546070701100532</v>
       </c>
       <c r="EQ9" t="n">
         <v>0</v>
       </c>
       <c r="ER9" t="n">
-        <v>-0.08687493060484995</v>
+        <v>-0.1216087002410595</v>
       </c>
       <c r="ES9" t="n">
-        <v>-0.06719102548698921</v>
+        <v>-0.005274432688134204</v>
       </c>
       <c r="ET9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV9" t="n">
         <v>0</v>
@@ -5444,25 +5444,25 @@
         <v>-0</v>
       </c>
       <c r="EY9" t="n">
-        <v>-0.1501070315676761</v>
+        <v>-0.08250256362436841</v>
       </c>
       <c r="EZ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA9" t="n">
-        <v>0.06241821846399533</v>
+        <v>0.1712596725889972</v>
       </c>
       <c r="FB9" t="n">
-        <v>-0.02157035122829993</v>
+        <v>0.02511802203699368</v>
       </c>
       <c r="FC9" t="n">
         <v>-0</v>
       </c>
       <c r="FD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF9" t="n">
         <v>0</v>
@@ -5471,49 +5471,49 @@
         <v>-0</v>
       </c>
       <c r="FH9" t="n">
-        <v>-0.05005834376978698</v>
+        <v>-0.03405060718224693</v>
       </c>
       <c r="FI9" t="n">
         <v>-0</v>
       </c>
       <c r="FJ9" t="n">
-        <v>0.0721439938969311</v>
+        <v>0.003032741133678719</v>
       </c>
       <c r="FK9" t="n">
-        <v>0.03937944302180001</v>
+        <v>-0.02353232346899969</v>
       </c>
       <c r="FL9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FM9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN9" t="n">
         <v>-0</v>
       </c>
       <c r="FO9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP9" t="n">
         <v>-0</v>
       </c>
       <c r="FQ9" t="n">
-        <v>-0.03035899399370516</v>
+        <v>0.05852313363767562</v>
       </c>
       <c r="FR9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS9" t="n">
-        <v>-0.02975089529408369</v>
+        <v>0.150472109661133</v>
       </c>
       <c r="FT9" t="n">
-        <v>-0.009005417133800911</v>
+        <v>-0.1557841122604667</v>
       </c>
       <c r="FU9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW9" t="n">
         <v>0</v>
@@ -5522,16 +5522,16 @@
         <v>0</v>
       </c>
       <c r="FY9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ9" t="n">
-        <v>-0.02594386750316973</v>
+        <v>0.003614636740359098</v>
       </c>
       <c r="GA9" t="n">
         <v>-0</v>
       </c>
       <c r="GB9" t="n">
-        <v>-0.02751552958082749</v>
+        <v>0.03144930263484152</v>
       </c>
       <c r="GC9" t="n">
         <v>0</v>
@@ -5543,10 +5543,10 @@
         <v>-0</v>
       </c>
       <c r="GF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -5554,16 +5554,16 @@
         <v>0</v>
       </c>
       <c r="B10" t="n">
-        <v>0.6869700235314398</v>
+        <v>0.1465475231184908</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.1362645646774766</v>
+        <v>-0.1323892330863067</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.07690094063131779</v>
+        <v>-0.06952872158433342</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -5572,25 +5572,25 @@
         <v>-0</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.02415384009197827</v>
+        <v>-0.01723359958842127</v>
       </c>
       <c r="I10" t="n">
         <v>-0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K10" t="n">
-        <v>0.3420461369198274</v>
+        <v>0.1070394719976259</v>
       </c>
       <c r="L10" t="n">
         <v>-0</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.09074323321808823</v>
+        <v>-0.1151885015826234</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.1759974349326422</v>
+        <v>-0.09018582633592322</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -5599,133 +5599,133 @@
         <v>-0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.00938184017735154</v>
+        <v>0.001968752986083979</v>
       </c>
       <c r="R10" t="n">
         <v>-0</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T10" t="n">
-        <v>0.2193554663343703</v>
+        <v>0.07779901270186147</v>
       </c>
       <c r="U10" t="n">
         <v>-0</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.1367914396971323</v>
+        <v>-0.04432955171988514</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.07713089179106057</v>
+        <v>-0.1167686333342908</v>
       </c>
       <c r="X10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>-7.008513872681143e-11</v>
+        <v>-8.404873848566715e-12</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.142542997077879</v>
+        <v>-0.04333334104996257</v>
       </c>
       <c r="AD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.06575305261381925</v>
+        <v>-0.06478440842015998</v>
       </c>
       <c r="AF10" t="n">
-        <v>-0.01214416960312589</v>
+        <v>-0.1618036917474506</v>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.005134024116485788</v>
+        <v>0.02449364722023266</v>
       </c>
       <c r="AJ10" t="n">
         <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.09085557813994516</v>
+        <v>0.1410436045678677</v>
       </c>
       <c r="AM10" t="n">
         <v>-0</v>
       </c>
       <c r="AN10" t="n">
-        <v>-0.07446370065663506</v>
+        <v>-0.03589182231526689</v>
       </c>
       <c r="AO10" t="n">
-        <v>-0.1353564318758657</v>
+        <v>0.05564349337944629</v>
       </c>
       <c r="AP10" t="n">
         <v>0</v>
       </c>
       <c r="AQ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.0618322782107807</v>
+        <v>0.01987260510333302</v>
       </c>
       <c r="AS10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT10" t="n">
         <v>-0</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.191116870762824</v>
+        <v>0.2505844611443078</v>
       </c>
       <c r="AV10" t="n">
         <v>-0</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.0302975675253322</v>
+        <v>-0.1245489222557329</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.3310293416767897</v>
+        <v>-0.3688780977945977</v>
       </c>
       <c r="AY10" t="n">
         <v>-0</v>
       </c>
       <c r="AZ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA10" t="n">
-        <v>0.2230560703858607</v>
+        <v>-0.03978573504929236</v>
       </c>
       <c r="BB10" t="n">
         <v>-0</v>
       </c>
       <c r="BC10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.06273951919878755</v>
+        <v>-0.04580867370754736</v>
       </c>
       <c r="BE10" t="n">
         <v>0</v>
       </c>
       <c r="BF10" t="n">
-        <v>-0.1176572286792924</v>
+        <v>-0.06868798971687241</v>
       </c>
       <c r="BG10" t="n">
-        <v>-0.4891085189017859</v>
+        <v>-0.06329798891921924</v>
       </c>
       <c r="BH10" t="n">
         <v>0</v>
@@ -5734,34 +5734,34 @@
         <v>-0</v>
       </c>
       <c r="BJ10" t="n">
-        <v>-2.989378382788984e-11</v>
+        <v>1.722013301044922e-11</v>
       </c>
       <c r="BK10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.2323761852681508</v>
+        <v>0.02037100111346307</v>
       </c>
       <c r="BN10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.2228566657866879</v>
+        <v>0.1015475175516023</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.223535546308101</v>
+        <v>-0.01290608054956052</v>
       </c>
       <c r="BQ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS10" t="n">
-        <v>0.03613763517904909</v>
+        <v>0.0004127174795847486</v>
       </c>
       <c r="BT10" t="n">
         <v>-0</v>
@@ -5770,70 +5770,70 @@
         <v>-0</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.4579472164604338</v>
+        <v>0.1573369574410869</v>
       </c>
       <c r="BW10" t="n">
         <v>-0</v>
       </c>
       <c r="BX10" t="n">
-        <v>0.01719744993631778</v>
+        <v>-0.138415104770107</v>
       </c>
       <c r="BY10" t="n">
-        <v>-0.0005510801359476933</v>
+        <v>-0.1450126418017317</v>
       </c>
       <c r="BZ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA10" t="n">
         <v>-0</v>
       </c>
       <c r="CB10" t="n">
-        <v>-0.01606855296625019</v>
+        <v>-0.05202694310782371</v>
       </c>
       <c r="CC10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE10" t="n">
-        <v>-0.216121011952144</v>
+        <v>-0.05861338760703411</v>
       </c>
       <c r="CF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG10" t="n">
-        <v>0.05190893694310304</v>
+        <v>0.1583272987365636</v>
       </c>
       <c r="CH10" t="n">
-        <v>-0.04655584494165783</v>
+        <v>0.04346105661757053</v>
       </c>
       <c r="CI10" t="n">
         <v>-0</v>
       </c>
       <c r="CJ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK10" t="n">
-        <v>-0.02583465904111515</v>
+        <v>-0.0188615065386466</v>
       </c>
       <c r="CL10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM10" t="n">
         <v>0</v>
       </c>
       <c r="CN10" t="n">
-        <v>-0.05136623287953734</v>
+        <v>-0.008726289874335611</v>
       </c>
       <c r="CO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP10" t="n">
-        <v>-0.0776625920572044</v>
+        <v>0.07274360642867743</v>
       </c>
       <c r="CQ10" t="n">
-        <v>-0.02833945425561048</v>
+        <v>0.1645909081766856</v>
       </c>
       <c r="CR10" t="n">
         <v>0</v>
@@ -5842,25 +5842,25 @@
         <v>-0</v>
       </c>
       <c r="CT10" t="n">
-        <v>0.07829615207160358</v>
+        <v>0.04490890681625587</v>
       </c>
       <c r="CU10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW10" t="n">
-        <v>-0.1593730963376644</v>
+        <v>-0.05955298325914821</v>
       </c>
       <c r="CX10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY10" t="n">
-        <v>0.1089233038446046</v>
+        <v>0.170078704485281</v>
       </c>
       <c r="CZ10" t="n">
-        <v>-0.06097824766009352</v>
+        <v>0.05652595712261352</v>
       </c>
       <c r="DA10" t="n">
         <v>0</v>
@@ -5869,106 +5869,106 @@
         <v>0</v>
       </c>
       <c r="DC10" t="n">
-        <v>-0.0260535628537003</v>
+        <v>-0.006225732103966068</v>
       </c>
       <c r="DD10" t="n">
         <v>-0</v>
       </c>
       <c r="DE10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF10" t="n">
-        <v>-0.1641368043707782</v>
+        <v>-0.06955763099470669</v>
       </c>
       <c r="DG10" t="n">
         <v>0</v>
       </c>
       <c r="DH10" t="n">
-        <v>0.07838048226093594</v>
+        <v>0.06507140565977942</v>
       </c>
       <c r="DI10" t="n">
-        <v>-0.007396624671875089</v>
+        <v>0.0008543626911686713</v>
       </c>
       <c r="DJ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.02913511091963766</v>
+        <v>-0.03796937672949457</v>
       </c>
       <c r="DM10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN10" t="n">
         <v>-0</v>
       </c>
       <c r="DO10" t="n">
-        <v>-0.1281027042752379</v>
+        <v>-0.03328737138661262</v>
       </c>
       <c r="DP10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ10" t="n">
-        <v>0.06624615972911323</v>
+        <v>0.09977933479163516</v>
       </c>
       <c r="DR10" t="n">
-        <v>0.01837350844511012</v>
+        <v>-0.07351586097364743</v>
       </c>
       <c r="DS10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT10" t="n">
         <v>-0</v>
       </c>
       <c r="DU10" t="n">
-        <v>0.07340545796154073</v>
+        <v>0.07275212180887439</v>
       </c>
       <c r="DV10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DX10" t="n">
-        <v>-0.1256233657481082</v>
+        <v>0.04028557295913131</v>
       </c>
       <c r="DY10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ10" t="n">
-        <v>-0.02726989794553657</v>
+        <v>0.1053299354315708</v>
       </c>
       <c r="EA10" t="n">
-        <v>-0.1484445550072378</v>
+        <v>-0.09283853431941205</v>
       </c>
       <c r="EB10" t="n">
         <v>-0</v>
       </c>
       <c r="EC10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED10" t="n">
-        <v>-0.003122181692385219</v>
+        <v>0.1244451874524875</v>
       </c>
       <c r="EE10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF10" t="n">
         <v>0</v>
       </c>
       <c r="EG10" t="n">
-        <v>-0.1402300293983871</v>
+        <v>0.01812521701866954</v>
       </c>
       <c r="EH10" t="n">
         <v>-0</v>
       </c>
       <c r="EI10" t="n">
-        <v>0.01127651985711733</v>
+        <v>0.1117393558107369</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.02915403829947535</v>
+        <v>0.01370004983135147</v>
       </c>
       <c r="EK10" t="n">
         <v>-0</v>
@@ -5977,7 +5977,7 @@
         <v>-0</v>
       </c>
       <c r="EM10" t="n">
-        <v>0.05580185365315857</v>
+        <v>-0.02122303866349485</v>
       </c>
       <c r="EN10" t="n">
         <v>0</v>
@@ -5986,133 +5986,133 @@
         <v>0</v>
       </c>
       <c r="EP10" t="n">
-        <v>-0.1803357861926596</v>
+        <v>-0.05090926489682848</v>
       </c>
       <c r="EQ10" t="n">
         <v>-0</v>
       </c>
       <c r="ER10" t="n">
-        <v>0.1351439222947043</v>
+        <v>0.1490072845489595</v>
       </c>
       <c r="ES10" t="n">
-        <v>-0.1939045102390745</v>
+        <v>-0.001022832409985937</v>
       </c>
       <c r="ET10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV10" t="n">
-        <v>-0.1591043228401461</v>
+        <v>0.03675751893919348</v>
       </c>
       <c r="EW10" t="n">
         <v>-0</v>
       </c>
       <c r="EX10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY10" t="n">
-        <v>-0.1690817893792273</v>
+        <v>-0.07360970255925005</v>
       </c>
       <c r="EZ10" t="n">
         <v>0</v>
       </c>
       <c r="FA10" t="n">
-        <v>0.07214574380907757</v>
+        <v>0.1941745616962877</v>
       </c>
       <c r="FB10" t="n">
-        <v>-0.0102227895213166</v>
+        <v>0.05300922553681649</v>
       </c>
       <c r="FC10" t="n">
         <v>-0</v>
       </c>
       <c r="FD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE10" t="n">
-        <v>-0.03039747996261594</v>
+        <v>-0.01177226512361096</v>
       </c>
       <c r="FF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH10" t="n">
-        <v>-0.05846536284039611</v>
+        <v>-0.02447592204449045</v>
       </c>
       <c r="FI10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ10" t="n">
-        <v>-0.1024899451519237</v>
+        <v>-0.01418951142891357</v>
       </c>
       <c r="FK10" t="n">
-        <v>0.003317974894237005</v>
+        <v>0.06434155846529468</v>
       </c>
       <c r="FL10" t="n">
         <v>0</v>
       </c>
       <c r="FM10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN10" t="n">
-        <v>-0.008417475965385269</v>
+        <v>-0.03143177472200972</v>
       </c>
       <c r="FO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ10" t="n">
-        <v>-0.2605001045357414</v>
+        <v>0.03078403906338012</v>
       </c>
       <c r="FR10" t="n">
         <v>0</v>
       </c>
       <c r="FS10" t="n">
-        <v>-0.1408660748550417</v>
+        <v>0.1846010174798433</v>
       </c>
       <c r="FT10" t="n">
-        <v>-0.3113071784378521</v>
+        <v>-0.1623181780793724</v>
       </c>
       <c r="FU10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV10" t="n">
         <v>-0</v>
       </c>
       <c r="FW10" t="n">
-        <v>-0.07342583844271411</v>
+        <v>-0.1108367642095457</v>
       </c>
       <c r="FX10" t="n">
         <v>0</v>
       </c>
       <c r="FY10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ10" t="n">
-        <v>-0.1309562661573855</v>
+        <v>-0.001298641043555317</v>
       </c>
       <c r="GA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB10" t="n">
-        <v>-0.067743977471367</v>
+        <v>0.08286071943713461</v>
       </c>
       <c r="GC10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE10" t="n">
         <v>-0</v>
       </c>
       <c r="GF10" t="n">
-        <v>0.05097908552330371</v>
+        <v>-0.03602313589705056</v>
       </c>
       <c r="GG10" t="n">
         <v>-0</v>
@@ -6123,22 +6123,22 @@
         <v>0</v>
       </c>
       <c r="B11" t="n">
-        <v>0.1347300408599199</v>
+        <v>0.3628553173749014</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.0249153128064625</v>
+        <v>-0.01818439176927398</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.1659445080791704</v>
+        <v>-0.2845516538390789</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H11" t="n">
         <v>-0</v>
@@ -6150,7 +6150,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0.08867673692351241</v>
+        <v>0.368716701852085</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -6159,16 +6159,16 @@
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.02371001451897194</v>
+        <v>-0.1171928790265441</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.1381260543805539</v>
+        <v>-0.2485267491106975</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -6177,7 +6177,7 @@
         <v>-0</v>
       </c>
       <c r="T11" t="n">
-        <v>0.01404557809125185</v>
+        <v>0.1536207607177338</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
@@ -6186,37 +6186,37 @@
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0.0007294884743956842</v>
+        <v>-0.1633318468786023</v>
       </c>
       <c r="X11" t="n">
-        <v>0.009807155261823974</v>
+        <v>-0.04000653164499968</v>
       </c>
       <c r="Y11" t="n">
         <v>-0</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.03418093176553114</v>
+        <v>0.06343055841703808</v>
       </c>
       <c r="AD11" t="n">
         <v>-0</v>
       </c>
       <c r="AE11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.02748702590066394</v>
+        <v>-0.3588823079661869</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.0002011714281932898</v>
+        <v>-0.0175489687757601</v>
       </c>
       <c r="AH11" t="n">
         <v>-0</v>
@@ -6231,7 +6231,7 @@
         <v>0</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.03013721116641525</v>
+        <v>0.1654696425161936</v>
       </c>
       <c r="AM11" t="n">
         <v>0</v>
@@ -6240,13 +6240,13 @@
         <v>0</v>
       </c>
       <c r="AO11" t="n">
-        <v>-0.004203872645900671</v>
+        <v>0.03107890588772201</v>
       </c>
       <c r="AP11" t="n">
-        <v>-0.02790468763489192</v>
+        <v>-0.05667464145232268</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR11" t="n">
         <v>-0</v>
@@ -6255,22 +6255,22 @@
         <v>0</v>
       </c>
       <c r="AT11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.1742974666012861</v>
+        <v>0.6562825424131515</v>
       </c>
       <c r="AV11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW11" t="n">
         <v>0</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.004381491078784477</v>
+        <v>-0.304633953077626</v>
       </c>
       <c r="AY11" t="n">
-        <v>-0.09504702656342084</v>
+        <v>-0.1712116946903204</v>
       </c>
       <c r="AZ11" t="n">
         <v>0</v>
@@ -6279,55 +6279,55 @@
         <v>-0</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC11" t="n">
         <v>0</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.06391240547014018</v>
+        <v>0.01157890888554025</v>
       </c>
       <c r="BE11" t="n">
         <v>0</v>
       </c>
       <c r="BF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BG11" t="n">
-        <v>-0.08288946062015128</v>
+        <v>-0.102827826553858</v>
       </c>
       <c r="BH11" t="n">
-        <v>-0.1043455480660155</v>
+        <v>-0.1753782639570093</v>
       </c>
       <c r="BI11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK11" t="n">
         <v>0</v>
       </c>
       <c r="BL11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.07630898564369155</v>
+        <v>0.07442403868462384</v>
       </c>
       <c r="BN11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO11" t="n">
         <v>-0</v>
       </c>
       <c r="BP11" t="n">
-        <v>0.02752833915084387</v>
+        <v>0.09033333205687602</v>
       </c>
       <c r="BQ11" t="n">
-        <v>0.000424984775708481</v>
+        <v>0.01049380150209445</v>
       </c>
       <c r="BR11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS11" t="n">
         <v>0</v>
@@ -6339,7 +6339,7 @@
         <v>-0</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.04655326402656153</v>
+        <v>0.3333521686487391</v>
       </c>
       <c r="BW11" t="n">
         <v>0</v>
@@ -6348,13 +6348,13 @@
         <v>0</v>
       </c>
       <c r="BY11" t="n">
-        <v>-0.01333984320775199</v>
+        <v>-0.0854293541253191</v>
       </c>
       <c r="BZ11" t="n">
-        <v>-0.03362606845280364</v>
+        <v>-0.1525171271304067</v>
       </c>
       <c r="CA11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB11" t="n">
         <v>-0</v>
@@ -6366,22 +6366,22 @@
         <v>-0</v>
       </c>
       <c r="CE11" t="n">
-        <v>-0.03737673854507382</v>
+        <v>-0.2014970807548995</v>
       </c>
       <c r="CF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG11" t="n">
         <v>-0</v>
       </c>
       <c r="CH11" t="n">
-        <v>0.001793858368082992</v>
+        <v>0.01503321050297434</v>
       </c>
       <c r="CI11" t="n">
-        <v>0.05095210987821867</v>
+        <v>0.1412148358900813</v>
       </c>
       <c r="CJ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK11" t="n">
         <v>0</v>
@@ -6393,61 +6393,61 @@
         <v>0</v>
       </c>
       <c r="CN11" t="n">
-        <v>0.0001536437162828128</v>
+        <v>-0.1583330663129932</v>
       </c>
       <c r="CO11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ11" t="n">
-        <v>0.01434202890246692</v>
+        <v>0.1381345976348538</v>
       </c>
       <c r="CR11" t="n">
-        <v>-0.008016696951351517</v>
+        <v>0.08681874560834207</v>
       </c>
       <c r="CS11" t="n">
         <v>-0</v>
       </c>
       <c r="CT11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV11" t="n">
         <v>0</v>
       </c>
       <c r="CW11" t="n">
-        <v>-0.02341630369968667</v>
+        <v>-0.1807988615787897</v>
       </c>
       <c r="CX11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY11" t="n">
         <v>0</v>
       </c>
       <c r="CZ11" t="n">
-        <v>0.004150579610847913</v>
+        <v>0.008864328042987544</v>
       </c>
       <c r="DA11" t="n">
-        <v>0.04873571698645011</v>
+        <v>0.1466253341874676</v>
       </c>
       <c r="DB11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC11" t="n">
         <v>-0</v>
       </c>
       <c r="DD11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE11" t="n">
         <v>0</v>
       </c>
       <c r="DF11" t="n">
-        <v>-0.008689004046524007</v>
+        <v>-0.06639972563559252</v>
       </c>
       <c r="DG11" t="n">
         <v>-0</v>
@@ -6456,10 +6456,10 @@
         <v>-0</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.02734967021459933</v>
+        <v>-0.1941117113926529</v>
       </c>
       <c r="DJ11" t="n">
-        <v>0.006302651131447227</v>
+        <v>0.0143172358351539</v>
       </c>
       <c r="DK11" t="n">
         <v>0</v>
@@ -6468,67 +6468,67 @@
         <v>0</v>
       </c>
       <c r="DM11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN11" t="n">
         <v>-0</v>
       </c>
       <c r="DO11" t="n">
-        <v>-0.009335295600809437</v>
+        <v>-0.07818441144243483</v>
       </c>
       <c r="DP11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR11" t="n">
-        <v>0.01952249801939772</v>
+        <v>-0.02316169977694305</v>
       </c>
       <c r="DS11" t="n">
-        <v>-0.02006855734031757</v>
+        <v>0.06727657276356383</v>
       </c>
       <c r="DT11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU11" t="n">
         <v>-0</v>
       </c>
       <c r="DV11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW11" t="n">
         <v>-0</v>
       </c>
       <c r="DX11" t="n">
-        <v>-0.001965625460674081</v>
+        <v>0.06140555030986562</v>
       </c>
       <c r="DY11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA11" t="n">
-        <v>-0.01796562514523701</v>
+        <v>0.003210881730700579</v>
       </c>
       <c r="EB11" t="n">
-        <v>0.01753195500138644</v>
+        <v>0.1077220975278129</v>
       </c>
       <c r="EC11" t="n">
         <v>-0</v>
       </c>
       <c r="ED11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE11" t="n">
         <v>-0</v>
       </c>
       <c r="EF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG11" t="n">
-        <v>-0.01310532564981117</v>
+        <v>-0.02241013156893051</v>
       </c>
       <c r="EH11" t="n">
         <v>0</v>
@@ -6537,106 +6537,106 @@
         <v>0</v>
       </c>
       <c r="EJ11" t="n">
-        <v>0.001128612767112992</v>
+        <v>-0.06786537678440173</v>
       </c>
       <c r="EK11" t="n">
-        <v>0.04068549638999126</v>
+        <v>0.07729333829914209</v>
       </c>
       <c r="EL11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN11" t="n">
         <v>0</v>
       </c>
       <c r="EO11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP11" t="n">
-        <v>-0.01753953731097314</v>
+        <v>-0.07326030060447609</v>
       </c>
       <c r="EQ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER11" t="n">
         <v>-0</v>
       </c>
       <c r="ES11" t="n">
-        <v>0.005289292238646263</v>
+        <v>-0.1099869125682123</v>
       </c>
       <c r="ET11" t="n">
-        <v>0.03993878276897259</v>
+        <v>0.1377504652391752</v>
       </c>
       <c r="EU11" t="n">
         <v>-0</v>
       </c>
       <c r="EV11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX11" t="n">
         <v>-0</v>
       </c>
       <c r="EY11" t="n">
-        <v>-0.02181313994298053</v>
+        <v>-0.2178112342559944</v>
       </c>
       <c r="EZ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA11" t="n">
         <v>-0</v>
       </c>
       <c r="FB11" t="n">
-        <v>0.003886528595353404</v>
+        <v>-0.009357877249979515</v>
       </c>
       <c r="FC11" t="n">
-        <v>0.0520346172835979</v>
+        <v>0.1244701948507584</v>
       </c>
       <c r="FD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE11" t="n">
         <v>0</v>
       </c>
       <c r="FF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG11" t="n">
         <v>0</v>
       </c>
       <c r="FH11" t="n">
-        <v>-0.01913052365622165</v>
+        <v>-0.2514990124052147</v>
       </c>
       <c r="FI11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ11" t="n">
         <v>-0</v>
       </c>
       <c r="FK11" t="n">
-        <v>-0.02276901203379851</v>
+        <v>0.1447317750094317</v>
       </c>
       <c r="FL11" t="n">
-        <v>0.02137787295572329</v>
+        <v>0.1625787867570504</v>
       </c>
       <c r="FM11" t="n">
         <v>0</v>
       </c>
       <c r="FN11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO11" t="n">
         <v>0</v>
       </c>
       <c r="FP11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ11" t="n">
-        <v>0.001371583198682368</v>
+        <v>0.1883399901373113</v>
       </c>
       <c r="FR11" t="n">
         <v>0</v>
@@ -6645,37 +6645,37 @@
         <v>-0</v>
       </c>
       <c r="FT11" t="n">
-        <v>-0.03733290112620254</v>
+        <v>-0.02942125917274895</v>
       </c>
       <c r="FU11" t="n">
-        <v>0.04545921202299252</v>
+        <v>0.1291485256699805</v>
       </c>
       <c r="FV11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ11" t="n">
-        <v>-0.02824886983961931</v>
+        <v>-0.03005954126737632</v>
       </c>
       <c r="GA11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB11" t="n">
         <v>-0</v>
       </c>
       <c r="GC11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD11" t="n">
-        <v>-0.008983276966860538</v>
+        <v>0.08048842957750643</v>
       </c>
       <c r="GE11" t="n">
         <v>-0</v>
@@ -6692,16 +6692,16 @@
         <v>0</v>
       </c>
       <c r="B12" t="n">
-        <v>0.2606693261802883</v>
+        <v>0.3228631664841062</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.1016151010760093</v>
+        <v>-0.1744836616547953</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.04817645896015755</v>
+        <v>-0.009450030700722775</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -6719,16 +6719,16 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1576315329367835</v>
+        <v>0.2904559874696415</v>
       </c>
       <c r="L12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.06970628532037529</v>
+        <v>-0.1607040462089321</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.06237009183842442</v>
+        <v>-0.06666237473625113</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -6737,34 +6737,34 @@
         <v>-0</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T12" t="n">
-        <v>0.08700822917191924</v>
+        <v>0.09898321021425545</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.02153960396990358</v>
+        <v>-0.05179190597137408</v>
       </c>
       <c r="W12" t="n">
-        <v>0.02874406879790403</v>
+        <v>-0.06174346385481731</v>
       </c>
       <c r="X12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
         <v>-0</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -6773,22 +6773,22 @@
         <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.09080062781673411</v>
+        <v>-0.1070140382228847</v>
       </c>
       <c r="AD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>-0.007404999100347285</v>
+        <v>-0.1223647590332389</v>
       </c>
       <c r="AF12" t="n">
-        <v>-0.02561094436282868</v>
+        <v>-0.1166652346175298</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
         <v>-0</v>
@@ -6800,52 +6800,52 @@
         <v>0</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.04697521275757512</v>
+        <v>0.1469974275233813</v>
       </c>
       <c r="AM12" t="n">
         <v>0</v>
       </c>
       <c r="AN12" t="n">
-        <v>-0.0371254922559633</v>
+        <v>-0.1309428660062221</v>
       </c>
       <c r="AO12" t="n">
-        <v>-0.05776555832130424</v>
+        <v>0.1015791575711294</v>
       </c>
       <c r="AP12" t="n">
         <v>0</v>
       </c>
       <c r="AQ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS12" t="n">
         <v>0</v>
       </c>
       <c r="AT12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.39932542257895</v>
+        <v>0.3292016936221337</v>
       </c>
       <c r="AV12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW12" t="n">
-        <v>-0.01205072722961664</v>
+        <v>-0.1652306580832631</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.08741064467908376</v>
+        <v>-0.2123345029737378</v>
       </c>
       <c r="AY12" t="n">
         <v>-0</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB12" t="n">
         <v>-0</v>
@@ -6854,25 +6854,25 @@
         <v>0</v>
       </c>
       <c r="BD12" t="n">
-        <v>-0.01522106442685801</v>
+        <v>-0.01250132894410522</v>
       </c>
       <c r="BE12" t="n">
         <v>0</v>
       </c>
       <c r="BF12" t="n">
-        <v>-0.07557924278152156</v>
+        <v>-0.05020627219169811</v>
       </c>
       <c r="BG12" t="n">
-        <v>-0.1660486117540314</v>
+        <v>-0.05616752213867007</v>
       </c>
       <c r="BH12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BI12" t="n">
         <v>-0</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK12" t="n">
         <v>0</v>
@@ -6881,49 +6881,49 @@
         <v>-0</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.07013395203734345</v>
+        <v>-0.04176724427030835</v>
       </c>
       <c r="BN12" t="n">
         <v>-0</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.07904927981747747</v>
+        <v>0.04977817645841364</v>
       </c>
       <c r="BP12" t="n">
-        <v>0.07528239599808524</v>
+        <v>0.01992855921989446</v>
       </c>
       <c r="BQ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS12" t="n">
         <v>-0</v>
       </c>
       <c r="BT12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU12" t="n">
         <v>-0</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.1526655600451193</v>
+        <v>0.2097341211889442</v>
       </c>
       <c r="BW12" t="n">
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>-0.01627093826003122</v>
+        <v>-0.1282837937330209</v>
       </c>
       <c r="BY12" t="n">
-        <v>0.02190667613496294</v>
+        <v>-0.02085607274696294</v>
       </c>
       <c r="BZ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB12" t="n">
         <v>0</v>
@@ -6935,19 +6935,19 @@
         <v>-0</v>
       </c>
       <c r="CE12" t="n">
-        <v>-0.07696700289828416</v>
+        <v>-0.1435687118908229</v>
       </c>
       <c r="CF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG12" t="n">
-        <v>0.01118971039184901</v>
+        <v>0.1655705886666514</v>
       </c>
       <c r="CH12" t="n">
-        <v>-0.007064501212374149</v>
+        <v>-0.0003634817285910705</v>
       </c>
       <c r="CI12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CJ12" t="n">
         <v>-0</v>
@@ -6956,31 +6956,31 @@
         <v>0</v>
       </c>
       <c r="CL12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM12" t="n">
         <v>0</v>
       </c>
       <c r="CN12" t="n">
-        <v>-0.01265127564091282</v>
+        <v>-0.03262367911035163</v>
       </c>
       <c r="CO12" t="n">
         <v>-0</v>
       </c>
       <c r="CP12" t="n">
-        <v>-0.03299195729651795</v>
+        <v>0.1629573949246584</v>
       </c>
       <c r="CQ12" t="n">
-        <v>-0.03960616712776534</v>
+        <v>0.04834896744458557</v>
       </c>
       <c r="CR12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS12" t="n">
         <v>-0</v>
       </c>
       <c r="CT12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU12" t="n">
         <v>-0</v>
@@ -6989,22 +6989,22 @@
         <v>0</v>
       </c>
       <c r="CW12" t="n">
-        <v>-0.05885498592827512</v>
+        <v>-0.1361996883242054</v>
       </c>
       <c r="CX12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY12" t="n">
-        <v>0.02916946500495316</v>
+        <v>0.1672359722918338</v>
       </c>
       <c r="CZ12" t="n">
-        <v>-0.009310012855968825</v>
+        <v>0.01425682615661594</v>
       </c>
       <c r="DA12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DB12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC12" t="n">
         <v>-0</v>
@@ -7016,22 +7016,22 @@
         <v>0</v>
       </c>
       <c r="DF12" t="n">
-        <v>-0.02119568349645119</v>
+        <v>-0.1063566294789613</v>
       </c>
       <c r="DG12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH12" t="n">
-        <v>0.01923899174257127</v>
+        <v>0.02337839846843453</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.01223155287151578</v>
+        <v>-0.1032200846718489</v>
       </c>
       <c r="DJ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL12" t="n">
         <v>0</v>
@@ -7040,22 +7040,22 @@
         <v>0</v>
       </c>
       <c r="DN12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO12" t="n">
-        <v>-0.03597177112006992</v>
+        <v>-0.0871749515930039</v>
       </c>
       <c r="DP12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ12" t="n">
-        <v>0.00749701465285287</v>
+        <v>0.08055498162388952</v>
       </c>
       <c r="DR12" t="n">
-        <v>-0.03921240405790868</v>
+        <v>0.003666242887684883</v>
       </c>
       <c r="DS12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT12" t="n">
         <v>-0</v>
@@ -7070,25 +7070,25 @@
         <v>-0</v>
       </c>
       <c r="DX12" t="n">
-        <v>0.006567906071782141</v>
+        <v>0.006249466032861034</v>
       </c>
       <c r="DY12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ12" t="n">
-        <v>0.01479469204650319</v>
+        <v>-0.08325497344666884</v>
       </c>
       <c r="EA12" t="n">
-        <v>-0.008795565147254663</v>
+        <v>0.0785708740201841</v>
       </c>
       <c r="EB12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE12" t="n">
         <v>-0</v>
@@ -7097,49 +7097,49 @@
         <v>0</v>
       </c>
       <c r="EG12" t="n">
-        <v>-0.03627573472256736</v>
+        <v>-0.09625458091450781</v>
       </c>
       <c r="EH12" t="n">
         <v>0</v>
       </c>
       <c r="EI12" t="n">
-        <v>0.02786256627911219</v>
+        <v>0.1465950809997594</v>
       </c>
       <c r="EJ12" t="n">
-        <v>0.02583137896142137</v>
+        <v>0.04114386099981716</v>
       </c>
       <c r="EK12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN12" t="n">
         <v>0</v>
       </c>
       <c r="EO12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP12" t="n">
-        <v>-0.07624089666060758</v>
+        <v>-0.08904537100973933</v>
       </c>
       <c r="EQ12" t="n">
         <v>0</v>
       </c>
       <c r="ER12" t="n">
-        <v>0.01855181402423942</v>
+        <v>0.1031802431584192</v>
       </c>
       <c r="ES12" t="n">
-        <v>0.02650950737420491</v>
+        <v>-0.0155808982504888</v>
       </c>
       <c r="ET12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV12" t="n">
         <v>0</v>
@@ -7151,94 +7151,94 @@
         <v>-0</v>
       </c>
       <c r="EY12" t="n">
-        <v>-0.06061832231539531</v>
+        <v>-0.1528334540266092</v>
       </c>
       <c r="EZ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA12" t="n">
-        <v>0.03433286848383905</v>
+        <v>0.1904292565772299</v>
       </c>
       <c r="FB12" t="n">
-        <v>-0.009172358160973865</v>
+        <v>-0.009483531886413302</v>
       </c>
       <c r="FC12" t="n">
         <v>-0</v>
       </c>
       <c r="FD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE12" t="n">
         <v>0</v>
       </c>
       <c r="FF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG12" t="n">
         <v>-0</v>
       </c>
       <c r="FH12" t="n">
-        <v>-0.01206752005854287</v>
+        <v>-0.1118424531371016</v>
       </c>
       <c r="FI12" t="n">
         <v>-0</v>
       </c>
       <c r="FJ12" t="n">
-        <v>0.05570938033153688</v>
+        <v>0.0749653671673589</v>
       </c>
       <c r="FK12" t="n">
-        <v>0.001635111456814837</v>
+        <v>0.003207476727769164</v>
       </c>
       <c r="FL12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FM12" t="n">
         <v>0</v>
       </c>
       <c r="FN12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP12" t="n">
         <v>-0</v>
       </c>
       <c r="FQ12" t="n">
-        <v>-0.01239890464590548</v>
+        <v>0.02658062363529577</v>
       </c>
       <c r="FR12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS12" t="n">
-        <v>0.03829363235404765</v>
+        <v>0.2049328438909383</v>
       </c>
       <c r="FT12" t="n">
-        <v>0.03743035436288289</v>
+        <v>0.04607689997364336</v>
       </c>
       <c r="FU12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW12" t="n">
         <v>0</v>
       </c>
       <c r="FX12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ12" t="n">
-        <v>0.03305766099681971</v>
+        <v>-0.1225114193251299</v>
       </c>
       <c r="GA12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB12" t="n">
-        <v>-0.04229761946889432</v>
+        <v>0.1161721493446113</v>
       </c>
       <c r="GC12" t="n">
         <v>0</v>
@@ -7250,18 +7250,18 @@
         <v>-0</v>
       </c>
       <c r="GF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B13" t="n">
-        <v>-0.4524744738400269</v>
+        <v>-0.1926610402608507</v>
       </c>
       <c r="C13" t="n">
         <v>-0</v>
@@ -7270,10 +7270,10 @@
         <v>-0</v>
       </c>
       <c r="E13" t="n">
-        <v>0.1993930184410106</v>
+        <v>0.03157909332238599</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9843475286947677</v>
+        <v>0.2039900211368087</v>
       </c>
       <c r="G13" t="n">
         <v>-0</v>
@@ -7288,7 +7288,7 @@
         <v>-0</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.2340035152068518</v>
+        <v>-0.1309598175964984</v>
       </c>
       <c r="L13" t="n">
         <v>-0</v>
@@ -7297,10 +7297,10 @@
         <v>-0</v>
       </c>
       <c r="N13" t="n">
-        <v>0.0007836314010653183</v>
+        <v>0.0776650751980455</v>
       </c>
       <c r="O13" t="n">
-        <v>0.7439530823450818</v>
+        <v>0.1473495937722647</v>
       </c>
       <c r="P13" t="n">
         <v>-0</v>
@@ -7315,46 +7315,46 @@
         <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>0.03162828027205047</v>
+        <v>-0.05590685979868402</v>
       </c>
       <c r="U13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
         <v>-0</v>
       </c>
       <c r="W13" t="n">
-        <v>0.4288577125932975</v>
+        <v>0.09068674442007549</v>
       </c>
       <c r="X13" t="n">
-        <v>0.1619128611731067</v>
+        <v>0.02478225096749651</v>
       </c>
       <c r="Y13" t="n">
         <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
         <v>-0</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AC13" t="n">
-        <v>-0.0430253452185585</v>
+        <v>0.01972887930172324</v>
       </c>
       <c r="AD13" t="n">
         <v>-0</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AF13" t="n">
-        <v>-0.1499035992772703</v>
+        <v>0.1930264903567112</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.1449196139008977</v>
+        <v>0.1483840632694449</v>
       </c>
       <c r="AH13" t="n">
         <v>-0</v>
@@ -7363,28 +7363,28 @@
         <v>0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK13" t="n">
         <v>-0</v>
       </c>
       <c r="AL13" t="n">
-        <v>-0.07971880006139673</v>
+        <v>-0.1197689390739296</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN13" t="n">
         <v>-0</v>
       </c>
       <c r="AO13" t="n">
-        <v>-0.00495444428336019</v>
+        <v>-0.04763839779533409</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.1719777156558851</v>
+        <v>0.08560200039817702</v>
       </c>
       <c r="AQ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR13" t="n">
         <v>0</v>
@@ -7393,10 +7393,10 @@
         <v>-0</v>
       </c>
       <c r="AT13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU13" t="n">
-        <v>-0.4178520770524299</v>
+        <v>-0.3199970885680551</v>
       </c>
       <c r="AV13" t="n">
         <v>0</v>
@@ -7405,10 +7405,10 @@
         <v>-0</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.5070554867361827</v>
+        <v>0.07372507405036199</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.8642880894718871</v>
+        <v>0.08984078942035059</v>
       </c>
       <c r="AZ13" t="n">
         <v>-0</v>
@@ -7417,13 +7417,13 @@
         <v>-0</v>
       </c>
       <c r="BB13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD13" t="n">
-        <v>-0.2339907058058919</v>
+        <v>0.04193095232241771</v>
       </c>
       <c r="BE13" t="n">
         <v>-0</v>
@@ -7432,40 +7432,40 @@
         <v>-0</v>
       </c>
       <c r="BG13" t="n">
-        <v>0.03766389699002643</v>
+        <v>0.1793790077956181</v>
       </c>
       <c r="BH13" t="n">
-        <v>0.3190629190553479</v>
+        <v>0.1610750775385021</v>
       </c>
       <c r="BI13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ13" t="n">
         <v>0</v>
       </c>
       <c r="BK13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BL13" t="n">
         <v>0</v>
       </c>
       <c r="BM13" t="n">
-        <v>-0.2553295012707476</v>
+        <v>0.02697344764970306</v>
       </c>
       <c r="BN13" t="n">
         <v>0</v>
       </c>
       <c r="BO13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP13" t="n">
-        <v>-0.05839065946569938</v>
+        <v>-0.07725785399743569</v>
       </c>
       <c r="BQ13" t="n">
-        <v>0.04497922245691629</v>
+        <v>-0.01075241515766276</v>
       </c>
       <c r="BR13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BS13" t="n">
         <v>-0</v>
@@ -7477,25 +7477,25 @@
         <v>0</v>
       </c>
       <c r="BV13" t="n">
-        <v>-0.130803971778029</v>
+        <v>-0.1055656402215368</v>
       </c>
       <c r="BW13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX13" t="n">
         <v>-0</v>
       </c>
       <c r="BY13" t="n">
-        <v>0.2124954773685888</v>
+        <v>0.02682273502996482</v>
       </c>
       <c r="BZ13" t="n">
-        <v>0.3628438696999676</v>
+        <v>0.1079470223385009</v>
       </c>
       <c r="CA13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CB13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC13" t="n">
         <v>-0</v>
@@ -7504,49 +7504,49 @@
         <v>0</v>
       </c>
       <c r="CE13" t="n">
-        <v>0.0975768101904525</v>
+        <v>0.1048889019565901</v>
       </c>
       <c r="CF13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CG13" t="n">
         <v>0</v>
       </c>
       <c r="CH13" t="n">
-        <v>-0.04628646724660439</v>
+        <v>-0.02620731365879227</v>
       </c>
       <c r="CI13" t="n">
-        <v>-0.264303245885934</v>
+        <v>-0.091264366620995</v>
       </c>
       <c r="CJ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK13" t="n">
         <v>-0</v>
       </c>
       <c r="CL13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CM13" t="n">
         <v>-0</v>
       </c>
       <c r="CN13" t="n">
-        <v>0.02688027063140011</v>
+        <v>0.148529770763938</v>
       </c>
       <c r="CO13" t="n">
         <v>-0</v>
       </c>
       <c r="CP13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CQ13" t="n">
-        <v>-0.1886799499604915</v>
+        <v>-0.1230863091523355</v>
       </c>
       <c r="CR13" t="n">
-        <v>0.03177468675672374</v>
+        <v>-0.07882532327289965</v>
       </c>
       <c r="CS13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT13" t="n">
         <v>0</v>
@@ -7558,22 +7558,22 @@
         <v>-0</v>
       </c>
       <c r="CW13" t="n">
-        <v>0.0673029339947509</v>
+        <v>0.09798690374053694</v>
       </c>
       <c r="CX13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CY13" t="n">
         <v>-0</v>
       </c>
       <c r="CZ13" t="n">
-        <v>-0.07502648703987792</v>
+        <v>-0.02475686291497209</v>
       </c>
       <c r="DA13" t="n">
-        <v>-0.2420546312679621</v>
+        <v>-0.08422994381780793</v>
       </c>
       <c r="DB13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC13" t="n">
         <v>0</v>
@@ -7585,100 +7585,100 @@
         <v>-0</v>
       </c>
       <c r="DF13" t="n">
-        <v>-0.04196941607963266</v>
+        <v>0.06869908767730085</v>
       </c>
       <c r="DG13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DI13" t="n">
-        <v>-0.2901062069929528</v>
+        <v>0.06748861937032663</v>
       </c>
       <c r="DJ13" t="n">
-        <v>-0.03293858526614166</v>
+        <v>-0.01905981243301388</v>
       </c>
       <c r="DK13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO13" t="n">
-        <v>-0.08763631920644503</v>
+        <v>0.05837706061026601</v>
       </c>
       <c r="DP13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DQ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DR13" t="n">
-        <v>-0.08656773993967191</v>
+        <v>0.01168185139779458</v>
       </c>
       <c r="DS13" t="n">
-        <v>-0.05192827270181594</v>
+        <v>-0.04227008949918008</v>
       </c>
       <c r="DT13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DX13" t="n">
-        <v>-0.01409853001784356</v>
+        <v>-0.02823862074929183</v>
       </c>
       <c r="DY13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EA13" t="n">
-        <v>-0.02917067132968236</v>
+        <v>0.001695348438271192</v>
       </c>
       <c r="EB13" t="n">
-        <v>-0.2139503710041671</v>
+        <v>-0.08151642595668943</v>
       </c>
       <c r="EC13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED13" t="n">
         <v>0</v>
       </c>
       <c r="EE13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EF13" t="n">
         <v>0</v>
       </c>
       <c r="EG13" t="n">
-        <v>0.1238813122715837</v>
+        <v>0.05566945580066163</v>
       </c>
       <c r="EH13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI13" t="n">
         <v>-0</v>
       </c>
       <c r="EJ13" t="n">
-        <v>-0.1414231399815537</v>
+        <v>0.001045174688868259</v>
       </c>
       <c r="EK13" t="n">
-        <v>-0.1989382104746961</v>
+        <v>-0.03846075918529505</v>
       </c>
       <c r="EL13" t="n">
         <v>0</v>
@@ -7687,55 +7687,55 @@
         <v>-0</v>
       </c>
       <c r="EN13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EP13" t="n">
-        <v>0.06770855687707007</v>
+        <v>0.02726907123411317</v>
       </c>
       <c r="EQ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER13" t="n">
         <v>0</v>
       </c>
       <c r="ES13" t="n">
-        <v>-0.05987693355387146</v>
+        <v>0.02260185890144007</v>
       </c>
       <c r="ET13" t="n">
-        <v>-0.2431476078939783</v>
+        <v>-0.06578984873451441</v>
       </c>
       <c r="EU13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV13" t="n">
         <v>-0</v>
       </c>
       <c r="EW13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX13" t="n">
         <v>0</v>
       </c>
       <c r="EY13" t="n">
-        <v>0.06218490599136178</v>
+        <v>0.1127588418707937</v>
       </c>
       <c r="EZ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FA13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB13" t="n">
-        <v>-0.1366929186514886</v>
+        <v>-0.01945387789304519</v>
       </c>
       <c r="FC13" t="n">
-        <v>-0.2426548916967398</v>
+        <v>-0.08392740088330898</v>
       </c>
       <c r="FD13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE13" t="n">
         <v>-0</v>
@@ -7747,7 +7747,7 @@
         <v>-0</v>
       </c>
       <c r="FH13" t="n">
-        <v>0.06376090243172866</v>
+        <v>0.1266591933106773</v>
       </c>
       <c r="FI13" t="n">
         <v>-0</v>
@@ -7756,25 +7756,25 @@
         <v>0</v>
       </c>
       <c r="FK13" t="n">
-        <v>-0.09304569712387202</v>
+        <v>-0.06691915902024052</v>
       </c>
       <c r="FL13" t="n">
-        <v>-0.03290203230402117</v>
+        <v>0.02820666457304907</v>
       </c>
       <c r="FM13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FP13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FQ13" t="n">
-        <v>-0.01457044888064034</v>
+        <v>-0.02478948143151653</v>
       </c>
       <c r="FR13" t="n">
         <v>0</v>
@@ -7783,10 +7783,10 @@
         <v>0</v>
       </c>
       <c r="FT13" t="n">
-        <v>-0.1301305952271133</v>
+        <v>0.002721873157810346</v>
       </c>
       <c r="FU13" t="n">
-        <v>0.07200702050141086</v>
+        <v>0.04749192899906238</v>
       </c>
       <c r="FV13" t="n">
         <v>0</v>
@@ -7795,31 +7795,31 @@
         <v>0</v>
       </c>
       <c r="FX13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FY13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FZ13" t="n">
-        <v>-0.005037992014031873</v>
+        <v>0.07296522582383841</v>
       </c>
       <c r="GA13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GC13" t="n">
         <v>-0</v>
       </c>
       <c r="GD13" t="n">
-        <v>-0.02290986848029922</v>
+        <v>-0.005790396859002993</v>
       </c>
       <c r="GE13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG13" t="n">
         <v>-0</v>
@@ -7827,34 +7827,34 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0.2070634505277382</v>
+        <v>0.1211407281720874</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C14" t="n">
         <v>-0</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.1527891103966427</v>
+        <v>-0.2259700204880312</v>
       </c>
       <c r="E14" t="n">
-        <v>0.139728663288919</v>
+        <v>0.06119051836944039</v>
       </c>
       <c r="F14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J14" t="n">
-        <v>0.1917258400045113</v>
+        <v>0.07345480424804739</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -7863,25 +7863,25 @@
         <v>-0</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.04985037874858319</v>
+        <v>-0.2489647685771842</v>
       </c>
       <c r="N14" t="n">
-        <v>0.07265805899522786</v>
+        <v>0.01180178171278852</v>
       </c>
       <c r="O14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S14" t="n">
-        <v>0.03951392609810863</v>
+        <v>-0.02075182520075773</v>
       </c>
       <c r="T14" t="n">
         <v>0</v>
@@ -7890,91 +7890,91 @@
         <v>-0</v>
       </c>
       <c r="V14" t="n">
-        <v>0.1158493505250817</v>
+        <v>-0.04601566016430563</v>
       </c>
       <c r="W14" t="n">
-        <v>0.07559995758532403</v>
+        <v>-0.05899608221467662</v>
       </c>
       <c r="X14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
         <v>-0</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA14" t="n">
         <v>-0</v>
       </c>
       <c r="AB14" t="n">
-        <v>-0.07514302565019154</v>
+        <v>0.03836159916892905</v>
       </c>
       <c r="AC14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE14" t="n">
-        <v>-0.05468898661808234</v>
+        <v>0.05814216846345032</v>
       </c>
       <c r="AF14" t="n">
-        <v>-0.03315903206327819</v>
+        <v>0.1747435259538449</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>-0.03081981300858528</v>
+        <v>0.03270711358065359</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN14" t="n">
-        <v>-0.02821140374572752</v>
+        <v>-0.1404576521224002</v>
       </c>
       <c r="AO14" t="n">
-        <v>-0.06527354417435588</v>
+        <v>0.04789065645693523</v>
       </c>
       <c r="AP14" t="n">
         <v>0</v>
       </c>
       <c r="AQ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS14" t="n">
         <v>-0</v>
       </c>
       <c r="AT14" t="n">
-        <v>0.1507135222550541</v>
+        <v>-0.06397084095699487</v>
       </c>
       <c r="AU14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AV14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW14" t="n">
-        <v>-0.06687335919845093</v>
+        <v>-0.3505869526169145</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.2616230709455466</v>
+        <v>-0.02230971754025507</v>
       </c>
       <c r="AY14" t="n">
         <v>-0</v>
@@ -7989,7 +7989,7 @@
         <v>-0</v>
       </c>
       <c r="BC14" t="n">
-        <v>0.2190484409978439</v>
+        <v>0.1661245603880065</v>
       </c>
       <c r="BD14" t="n">
         <v>0</v>
@@ -7998,37 +7998,37 @@
         <v>-0</v>
       </c>
       <c r="BF14" t="n">
-        <v>0.01422336449566378</v>
+        <v>0.2068981614639333</v>
       </c>
       <c r="BG14" t="n">
-        <v>0.05924868341714198</v>
+        <v>0.1684847092327525</v>
       </c>
       <c r="BH14" t="n">
         <v>0</v>
       </c>
       <c r="BI14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK14" t="n">
         <v>0</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.08814029639012623</v>
+        <v>-0.003613179619675863</v>
       </c>
       <c r="BM14" t="n">
         <v>0</v>
       </c>
       <c r="BN14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO14" t="n">
-        <v>0.03412363422752315</v>
+        <v>0.01389766238075032</v>
       </c>
       <c r="BP14" t="n">
-        <v>0.1706622831733927</v>
+        <v>-0.1089563399075943</v>
       </c>
       <c r="BQ14" t="n">
         <v>0</v>
@@ -8037,25 +8037,25 @@
         <v>0</v>
       </c>
       <c r="BS14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU14" t="n">
-        <v>0.0465102087152437</v>
+        <v>-0.04801164201136012</v>
       </c>
       <c r="BV14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BW14" t="n">
         <v>-0</v>
       </c>
       <c r="BX14" t="n">
-        <v>0.007585108612994046</v>
+        <v>-0.1967194947099738</v>
       </c>
       <c r="BY14" t="n">
-        <v>0.110756428040185</v>
+        <v>-0.03917618133221584</v>
       </c>
       <c r="BZ14" t="n">
         <v>0</v>
@@ -8064,13 +8064,13 @@
         <v>0</v>
       </c>
       <c r="CB14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CC14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD14" t="n">
-        <v>-0.03724474927715508</v>
+        <v>-0.05510357444304977</v>
       </c>
       <c r="CE14" t="n">
         <v>0</v>
@@ -8079,16 +8079,16 @@
         <v>0</v>
       </c>
       <c r="CG14" t="n">
-        <v>-0.02055046533162123</v>
+        <v>0.1077389389097189</v>
       </c>
       <c r="CH14" t="n">
-        <v>-0.0429480442387252</v>
+        <v>-0.02004315818429219</v>
       </c>
       <c r="CI14" t="n">
         <v>0</v>
       </c>
       <c r="CJ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK14" t="n">
         <v>0</v>
@@ -8097,61 +8097,61 @@
         <v>-0</v>
       </c>
       <c r="CM14" t="n">
-        <v>-0.05572466906644654</v>
+        <v>-0.0008004771742731702</v>
       </c>
       <c r="CN14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CO14" t="n">
         <v>-0</v>
       </c>
       <c r="CP14" t="n">
-        <v>-0.1332427231054665</v>
+        <v>0.1108377789218846</v>
       </c>
       <c r="CQ14" t="n">
-        <v>-0.1162277573287646</v>
+        <v>-0.04935645159439225</v>
       </c>
       <c r="CR14" t="n">
         <v>0</v>
       </c>
       <c r="CS14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU14" t="n">
         <v>-0</v>
       </c>
       <c r="CV14" t="n">
-        <v>-0.01667374347957047</v>
+        <v>-0.04688053165691792</v>
       </c>
       <c r="CW14" t="n">
         <v>-0</v>
       </c>
       <c r="CX14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CY14" t="n">
-        <v>0.006332038206917859</v>
+        <v>0.1095484196360995</v>
       </c>
       <c r="CZ14" t="n">
-        <v>-0.03487417398405242</v>
+        <v>-0.001650573257281331</v>
       </c>
       <c r="DA14" t="n">
         <v>-0</v>
       </c>
       <c r="DB14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC14" t="n">
         <v>-0</v>
       </c>
       <c r="DD14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE14" t="n">
-        <v>-0.02163093039542517</v>
+        <v>-0.00356116194881815</v>
       </c>
       <c r="DF14" t="n">
         <v>-0</v>
@@ -8160,10 +8160,10 @@
         <v>0</v>
       </c>
       <c r="DH14" t="n">
-        <v>0.07475444571538935</v>
+        <v>0.08129640828805447</v>
       </c>
       <c r="DI14" t="n">
-        <v>-0.03584592152099914</v>
+        <v>-0.01676680481950708</v>
       </c>
       <c r="DJ14" t="n">
         <v>0</v>
@@ -8178,7 +8178,7 @@
         <v>0</v>
       </c>
       <c r="DN14" t="n">
-        <v>-0.0502686641409219</v>
+        <v>-0.06579225939158799</v>
       </c>
       <c r="DO14" t="n">
         <v>-0</v>
@@ -8187,70 +8187,70 @@
         <v>0</v>
       </c>
       <c r="DQ14" t="n">
-        <v>0.0689678159436011</v>
+        <v>0.01358216993179534</v>
       </c>
       <c r="DR14" t="n">
-        <v>-0.1076274657611254</v>
+        <v>0.01236702613106507</v>
       </c>
       <c r="DS14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT14" t="n">
         <v>-0</v>
       </c>
       <c r="DU14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV14" t="n">
         <v>0</v>
       </c>
       <c r="DW14" t="n">
-        <v>-0.07151857677275862</v>
+        <v>0.01347315508193833</v>
       </c>
       <c r="DX14" t="n">
         <v>-0</v>
       </c>
       <c r="DY14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ14" t="n">
-        <v>-0.02347601385324561</v>
+        <v>0.01324501646482771</v>
       </c>
       <c r="EA14" t="n">
-        <v>-0.08979990174464668</v>
+        <v>0.02690201716855667</v>
       </c>
       <c r="EB14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF14" t="n">
-        <v>-0.03874323153515925</v>
+        <v>-0.08607162868138776</v>
       </c>
       <c r="EG14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EH14" t="n">
         <v>0</v>
       </c>
       <c r="EI14" t="n">
-        <v>0.02977845107568349</v>
+        <v>0.09918299477684325</v>
       </c>
       <c r="EJ14" t="n">
-        <v>0.01780462056955368</v>
+        <v>0.02006589166306759</v>
       </c>
       <c r="EK14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM14" t="n">
         <v>0</v>
@@ -8259,22 +8259,22 @@
         <v>-0</v>
       </c>
       <c r="EO14" t="n">
-        <v>0.01243484029829679</v>
+        <v>0.0279013410814376</v>
       </c>
       <c r="EP14" t="n">
         <v>0</v>
       </c>
       <c r="EQ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER14" t="n">
-        <v>0.03368536203129598</v>
+        <v>0.1194958974062769</v>
       </c>
       <c r="ES14" t="n">
-        <v>0.01847656782168937</v>
+        <v>0.01951838139490126</v>
       </c>
       <c r="ET14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU14" t="n">
         <v>0</v>
@@ -8286,34 +8286,34 @@
         <v>-0</v>
       </c>
       <c r="EX14" t="n">
-        <v>-0.02151086311395828</v>
+        <v>-0.05383611330695823</v>
       </c>
       <c r="EY14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EZ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FA14" t="n">
-        <v>-0.01032136593724652</v>
+        <v>0.1409603175517452</v>
       </c>
       <c r="FB14" t="n">
-        <v>-0.04605219388245954</v>
+        <v>-0.01163953021819537</v>
       </c>
       <c r="FC14" t="n">
         <v>0</v>
       </c>
       <c r="FD14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE14" t="n">
         <v>0</v>
       </c>
       <c r="FF14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FG14" t="n">
-        <v>-0.0426524212475698</v>
+        <v>0.01690408517940004</v>
       </c>
       <c r="FH14" t="n">
         <v>0</v>
@@ -8322,10 +8322,10 @@
         <v>-0</v>
       </c>
       <c r="FJ14" t="n">
-        <v>0.02823741710139682</v>
+        <v>0.09958957096224487</v>
       </c>
       <c r="FK14" t="n">
-        <v>-0.1862454436008055</v>
+        <v>0.1305197848836541</v>
       </c>
       <c r="FL14" t="n">
         <v>0</v>
@@ -8334,13 +8334,13 @@
         <v>-0</v>
       </c>
       <c r="FN14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO14" t="n">
         <v>-0</v>
       </c>
       <c r="FP14" t="n">
-        <v>0.007815398110875709</v>
+        <v>-0.006106269398164259</v>
       </c>
       <c r="FQ14" t="n">
         <v>-0</v>
@@ -8349,34 +8349,34 @@
         <v>-0</v>
       </c>
       <c r="FS14" t="n">
-        <v>-0.0285089755736265</v>
+        <v>0.2291507346583974</v>
       </c>
       <c r="FT14" t="n">
-        <v>0.07697554240654686</v>
+        <v>0.07460672935131413</v>
       </c>
       <c r="FU14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW14" t="n">
         <v>0</v>
       </c>
       <c r="FX14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FY14" t="n">
-        <v>0.03651876679948103</v>
+        <v>0.01987395830541937</v>
       </c>
       <c r="FZ14" t="n">
         <v>0</v>
       </c>
       <c r="GA14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB14" t="n">
-        <v>-0.0508204063516501</v>
+        <v>0.1903930481415776</v>
       </c>
       <c r="GC14" t="n">
         <v>0</v>
@@ -9537,22 +9537,22 @@
         <v>0</v>
       </c>
       <c r="B17" t="n">
-        <v>0.559524000778469</v>
+        <v>0.3129544858893787</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.2330714662812555</v>
+        <v>-0.1522348581145022</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.02770239934542904</v>
+        <v>-0.06054775312193345</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -9564,22 +9564,22 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0.3230855615148865</v>
+        <v>0.2967024060103832</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.2397277187806909</v>
+        <v>-0.2015315886581548</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.02953011226699564</v>
+        <v>-0.1093389791354686</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -9591,76 +9591,76 @@
         <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>0.120066479444405</v>
+        <v>0.03975427820473097</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.001989388732499831</v>
+        <v>-0.05146555047132426</v>
       </c>
       <c r="W17" t="n">
-        <v>0.1981399025553424</v>
+        <v>-0.07338353732334585</v>
       </c>
       <c r="X17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
         <v>-0</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.09296925325541129</v>
+        <v>-0.0722500547200715</v>
       </c>
       <c r="AD17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>0.05401021876134467</v>
+        <v>-0.09776391800451797</v>
       </c>
       <c r="AF17" t="n">
-        <v>-0.06264986771571722</v>
+        <v>-0.06291256572592854</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
         <v>0</v>
       </c>
       <c r="AL17" t="n">
-        <v>-0.01235659805607243</v>
+        <v>0.0969240921655647</v>
       </c>
       <c r="AM17" t="n">
         <v>-0</v>
       </c>
       <c r="AN17" t="n">
-        <v>-0.06100369606455219</v>
+        <v>-0.09965126744366093</v>
       </c>
       <c r="AO17" t="n">
-        <v>0.0002119291363684451</v>
+        <v>0.05204442113764492</v>
       </c>
       <c r="AP17" t="n">
         <v>0</v>
       </c>
       <c r="AQ17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR17" t="n">
         <v>-0</v>
@@ -9672,25 +9672,25 @@
         <v>0</v>
       </c>
       <c r="AU17" t="n">
-        <v>0.5098456828529349</v>
+        <v>0.2657099499193543</v>
       </c>
       <c r="AV17" t="n">
         <v>-0</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.09552904747648819</v>
+        <v>-0.0600998929872754</v>
       </c>
       <c r="AX17" t="n">
-        <v>0.1819136161770179</v>
+        <v>-0.1597602810296587</v>
       </c>
       <c r="AY17" t="n">
         <v>-0</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB17" t="n">
         <v>-0</v>
@@ -9699,25 +9699,25 @@
         <v>0</v>
       </c>
       <c r="BD17" t="n">
-        <v>0.08121509447588829</v>
+        <v>-0.006391949691019367</v>
       </c>
       <c r="BE17" t="n">
         <v>0</v>
       </c>
       <c r="BF17" t="n">
-        <v>-0.2667270040379431</v>
+        <v>-0.02478779232793465</v>
       </c>
       <c r="BG17" t="n">
-        <v>-0.186434618143963</v>
+        <v>-0.04449380173021578</v>
       </c>
       <c r="BH17" t="n">
         <v>0</v>
       </c>
       <c r="BI17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK17" t="n">
         <v>0</v>
@@ -9726,70 +9726,70 @@
         <v>-0</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.1251908454217623</v>
+        <v>-0.01179273096250095</v>
       </c>
       <c r="BN17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO17" t="n">
-        <v>-0.003148522337728738</v>
+        <v>0.05499549609912618</v>
       </c>
       <c r="BP17" t="n">
-        <v>0.2043354629318599</v>
+        <v>0.04739752902133432</v>
       </c>
       <c r="BQ17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS17" t="n">
         <v>-0</v>
       </c>
       <c r="BT17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU17" t="n">
         <v>0</v>
       </c>
       <c r="BV17" t="n">
-        <v>0.1528064659880441</v>
+        <v>0.1456380305265589</v>
       </c>
       <c r="BW17" t="n">
         <v>0</v>
       </c>
       <c r="BX17" t="n">
-        <v>0.03774634467414721</v>
+        <v>-0.09647464657329732</v>
       </c>
       <c r="BY17" t="n">
-        <v>0.1017985922537798</v>
+        <v>-0.02685765196501011</v>
       </c>
       <c r="BZ17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA17" t="n">
         <v>-0</v>
       </c>
       <c r="CB17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD17" t="n">
         <v>-0</v>
       </c>
       <c r="CE17" t="n">
-        <v>-0.1252460441192026</v>
+        <v>-0.1065988158494016</v>
       </c>
       <c r="CF17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG17" t="n">
-        <v>-0.005043077300149587</v>
+        <v>0.09202045237825149</v>
       </c>
       <c r="CH17" t="n">
-        <v>-0.02220350025576284</v>
+        <v>0.01385107251609353</v>
       </c>
       <c r="CI17" t="n">
         <v>-0</v>
@@ -9801,25 +9801,25 @@
         <v>0</v>
       </c>
       <c r="CL17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CM17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CN17" t="n">
-        <v>-0.001641613671571868</v>
+        <v>-0.06153989477416343</v>
       </c>
       <c r="CO17" t="n">
         <v>-0</v>
       </c>
       <c r="CP17" t="n">
-        <v>-0.234997905177404</v>
+        <v>0.1632184907034185</v>
       </c>
       <c r="CQ17" t="n">
-        <v>-0.08469055862311795</v>
+        <v>0.03710302634963917</v>
       </c>
       <c r="CR17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS17" t="n">
         <v>-0</v>
@@ -9834,43 +9834,43 @@
         <v>0</v>
       </c>
       <c r="CW17" t="n">
-        <v>-0.0891056202446842</v>
+        <v>-0.106157982701392</v>
       </c>
       <c r="CX17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY17" t="n">
-        <v>0.03755195343861334</v>
+        <v>0.09937784504360463</v>
       </c>
       <c r="CZ17" t="n">
-        <v>-0.03639352869303281</v>
+        <v>0.02520446763208374</v>
       </c>
       <c r="DA17" t="n">
         <v>0</v>
       </c>
       <c r="DB17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE17" t="n">
         <v>0</v>
       </c>
       <c r="DF17" t="n">
-        <v>-0.02845429717720982</v>
+        <v>-0.04766276393289846</v>
       </c>
       <c r="DG17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH17" t="n">
-        <v>0.08827535161278906</v>
+        <v>0.02720481866004532</v>
       </c>
       <c r="DI17" t="n">
-        <v>0.04361921855614237</v>
+        <v>-0.08619502799551179</v>
       </c>
       <c r="DJ17" t="n">
         <v>-0</v>
@@ -9885,28 +9885,28 @@
         <v>0</v>
       </c>
       <c r="DN17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO17" t="n">
-        <v>-0.08181816000405309</v>
+        <v>-0.05702110941019668</v>
       </c>
       <c r="DP17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ17" t="n">
-        <v>-0.02359114695772073</v>
+        <v>-0.0267844321647682</v>
       </c>
       <c r="DR17" t="n">
-        <v>-0.04949029273662999</v>
+        <v>-0.02575022804124076</v>
       </c>
       <c r="DS17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT17" t="n">
         <v>-0</v>
       </c>
       <c r="DU17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV17" t="n">
         <v>0</v>
@@ -9915,16 +9915,16 @@
         <v>-0</v>
       </c>
       <c r="DX17" t="n">
-        <v>-0.05132575569395859</v>
+        <v>-0.002414347075065819</v>
       </c>
       <c r="DY17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ17" t="n">
-        <v>-0.0520147183943462</v>
+        <v>0.07028128159804879</v>
       </c>
       <c r="EA17" t="n">
-        <v>-0.08288540225719272</v>
+        <v>-0.0007819913975252653</v>
       </c>
       <c r="EB17" t="n">
         <v>-0</v>
@@ -9933,52 +9933,52 @@
         <v>-0</v>
       </c>
       <c r="ED17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG17" t="n">
-        <v>-0.1034471576652698</v>
+        <v>-0.08158634206860667</v>
       </c>
       <c r="EH17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI17" t="n">
-        <v>-0.02708120228071764</v>
+        <v>0.06665113387132716</v>
       </c>
       <c r="EJ17" t="n">
-        <v>0.08740387655414349</v>
+        <v>0.06338811704014582</v>
       </c>
       <c r="EK17" t="n">
         <v>0</v>
       </c>
       <c r="EL17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM17" t="n">
         <v>0</v>
       </c>
       <c r="EN17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP17" t="n">
-        <v>0.009553618274564005</v>
+        <v>-0.04153981445491703</v>
       </c>
       <c r="EQ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER17" t="n">
-        <v>0.01987120470674911</v>
+        <v>0.06431711266781782</v>
       </c>
       <c r="ES17" t="n">
-        <v>0.01159875883617959</v>
+        <v>-0.004923844471995725</v>
       </c>
       <c r="ET17" t="n">
         <v>0</v>
@@ -9996,25 +9996,25 @@
         <v>-0</v>
       </c>
       <c r="EY17" t="n">
-        <v>-0.0855048522954759</v>
+        <v>-0.1121471316519863</v>
       </c>
       <c r="EZ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA17" t="n">
-        <v>-0.02447884065062331</v>
+        <v>0.1187886044090597</v>
       </c>
       <c r="FB17" t="n">
-        <v>-0.003702749208864165</v>
+        <v>0.006023998426831777</v>
       </c>
       <c r="FC17" t="n">
         <v>-0</v>
       </c>
       <c r="FD17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF17" t="n">
         <v>0</v>
@@ -10023,16 +10023,16 @@
         <v>0</v>
       </c>
       <c r="FH17" t="n">
-        <v>0.01479937446324157</v>
+        <v>0.1073044837231265</v>
       </c>
       <c r="FI17" t="n">
         <v>-0</v>
       </c>
       <c r="FJ17" t="n">
-        <v>-0.008459869775285591</v>
+        <v>0.07366274000973731</v>
       </c>
       <c r="FK17" t="n">
-        <v>-0.02279557559513727</v>
+        <v>0.01470913974689237</v>
       </c>
       <c r="FL17" t="n">
         <v>-0</v>
@@ -10044,28 +10044,28 @@
         <v>-0</v>
       </c>
       <c r="FO17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ17" t="n">
-        <v>-0.04621183659143154</v>
+        <v>0.04378216511573787</v>
       </c>
       <c r="FR17" t="n">
         <v>0</v>
       </c>
       <c r="FS17" t="n">
-        <v>0.03337502380121125</v>
+        <v>0.1042751487820166</v>
       </c>
       <c r="FT17" t="n">
-        <v>-0.05881057984368338</v>
+        <v>-0.01968128517293833</v>
       </c>
       <c r="FU17" t="n">
         <v>-0</v>
       </c>
       <c r="FV17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW17" t="n">
         <v>-0</v>
@@ -10074,25 +10074,25 @@
         <v>0</v>
       </c>
       <c r="FY17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ17" t="n">
-        <v>0.07406946616481051</v>
+        <v>-0.06692114248400161</v>
       </c>
       <c r="GA17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB17" t="n">
-        <v>-0.1428375052823531</v>
+        <v>0.03462950064163612</v>
       </c>
       <c r="GC17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF17" t="n">
         <v>0</v>
@@ -10106,7 +10106,7 @@
         <v>0</v>
       </c>
       <c r="B18" t="n">
-        <v>0.1508827158852239</v>
+        <v>0.2402173319976812</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
@@ -10115,25 +10115,25 @@
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.05540472024496717</v>
+        <v>0.001111593287612051</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.08895143080684446</v>
+        <v>-0.1102826193400708</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0.1136448567996548</v>
+        <v>0.2448689779845244</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -10142,67 +10142,67 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.03699303312441549</v>
+        <v>-0.06109390333548194</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.06991022176452612</v>
+        <v>-0.118317213545678</v>
       </c>
       <c r="P18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T18" t="n">
-        <v>0.01178140136480864</v>
+        <v>0.05990102900099524</v>
       </c>
       <c r="U18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.008926459609585118</v>
+        <v>-0.08081952019625631</v>
       </c>
       <c r="X18" t="n">
-        <v>0.01436220799389488</v>
+        <v>-0.005159166439724939</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA18" t="n">
         <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>-0.01322699201789526</v>
+        <v>-0.03180857135565417</v>
       </c>
       <c r="AD18" t="n">
         <v>-0</v>
       </c>
       <c r="AE18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.01653185008956016</v>
+        <v>-0.146242924045017</v>
       </c>
       <c r="AG18" t="n">
-        <v>0.004366665881559117</v>
+        <v>0.02679393606997117</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI18" t="n">
         <v>-0</v>
@@ -10214,22 +10214,22 @@
         <v>0</v>
       </c>
       <c r="AL18" t="n">
-        <v>0.008973212011039849</v>
+        <v>0.02234935147164802</v>
       </c>
       <c r="AM18" t="n">
         <v>-0</v>
       </c>
       <c r="AN18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO18" t="n">
-        <v>-0.01569315526480149</v>
+        <v>-0.03136037861295423</v>
       </c>
       <c r="AP18" t="n">
-        <v>-0.01367214951701976</v>
+        <v>0.003433125970518289</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR18" t="n">
         <v>-0</v>
@@ -10238,10 +10238,10 @@
         <v>0</v>
       </c>
       <c r="AT18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU18" t="n">
-        <v>0.1153938711451974</v>
+        <v>0.2022584681956612</v>
       </c>
       <c r="AV18" t="n">
         <v>-0</v>
@@ -10250,25 +10250,25 @@
         <v>0</v>
       </c>
       <c r="AX18" t="n">
-        <v>-0.01787878461818319</v>
+        <v>-0.1793802425088967</v>
       </c>
       <c r="AY18" t="n">
-        <v>-0.02147783924078349</v>
+        <v>-0.0778709800041215</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA18" t="n">
         <v>-0</v>
       </c>
       <c r="BB18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC18" t="n">
         <v>0</v>
       </c>
       <c r="BD18" t="n">
-        <v>0.04234387283958466</v>
+        <v>0.01781549608877071</v>
       </c>
       <c r="BE18" t="n">
         <v>0</v>
@@ -10277,13 +10277,13 @@
         <v>0</v>
       </c>
       <c r="BG18" t="n">
-        <v>-0.05423539485419909</v>
+        <v>0.002091080394419572</v>
       </c>
       <c r="BH18" t="n">
-        <v>-0.07088993894401294</v>
+        <v>-0.06049531310338922</v>
       </c>
       <c r="BI18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ18" t="n">
         <v>-0</v>
@@ -10292,37 +10292,37 @@
         <v>0</v>
       </c>
       <c r="BL18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.0439984694098617</v>
+        <v>0.0166954775618248</v>
       </c>
       <c r="BN18" t="n">
         <v>-0</v>
       </c>
       <c r="BO18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP18" t="n">
-        <v>0.02614911999761512</v>
+        <v>0.06494370061543805</v>
       </c>
       <c r="BQ18" t="n">
-        <v>0.02462848970999234</v>
+        <v>-0.003852677009463982</v>
       </c>
       <c r="BR18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS18" t="n">
         <v>-0</v>
       </c>
       <c r="BT18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV18" t="n">
-        <v>0.04266072859301578</v>
+        <v>0.08700227029725847</v>
       </c>
       <c r="BW18" t="n">
         <v>0</v>
@@ -10331,10 +10331,10 @@
         <v>0</v>
       </c>
       <c r="BY18" t="n">
-        <v>-0.008102824211839761</v>
+        <v>-0.03004847284499008</v>
       </c>
       <c r="BZ18" t="n">
-        <v>-0.003687665916994841</v>
+        <v>-0.0596120840302558</v>
       </c>
       <c r="CA18" t="n">
         <v>-0</v>
@@ -10343,28 +10343,28 @@
         <v>-0</v>
       </c>
       <c r="CC18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE18" t="n">
-        <v>-0.02642850495499472</v>
+        <v>-0.06768550786817001</v>
       </c>
       <c r="CF18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG18" t="n">
         <v>-0</v>
       </c>
       <c r="CH18" t="n">
-        <v>0.004260049307465665</v>
+        <v>0.0102279727609073</v>
       </c>
       <c r="CI18" t="n">
-        <v>0.02466206814603156</v>
+        <v>0.0434279463563787</v>
       </c>
       <c r="CJ18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK18" t="n">
         <v>-0</v>
@@ -10373,10 +10373,10 @@
         <v>0</v>
       </c>
       <c r="CM18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN18" t="n">
-        <v>-0.007458122977956908</v>
+        <v>-0.02329687057131838</v>
       </c>
       <c r="CO18" t="n">
         <v>-0</v>
@@ -10385,64 +10385,64 @@
         <v>-0</v>
       </c>
       <c r="CQ18" t="n">
-        <v>-0.0006786419483999593</v>
+        <v>0.09595889419233883</v>
       </c>
       <c r="CR18" t="n">
-        <v>-0.02317395392696445</v>
+        <v>0.06895874122066736</v>
       </c>
       <c r="CS18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW18" t="n">
-        <v>-0.02001764049277187</v>
+        <v>-0.06890462123330202</v>
       </c>
       <c r="CX18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY18" t="n">
         <v>0</v>
       </c>
       <c r="CZ18" t="n">
-        <v>0.007080366347209785</v>
+        <v>0.007130038803875816</v>
       </c>
       <c r="DA18" t="n">
-        <v>0.02416010117408244</v>
+        <v>0.05925594604669742</v>
       </c>
       <c r="DB18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE18" t="n">
         <v>-0</v>
       </c>
       <c r="DF18" t="n">
-        <v>-0.0165175536301642</v>
+        <v>-0.02047642494833745</v>
       </c>
       <c r="DG18" t="n">
         <v>-0</v>
       </c>
       <c r="DH18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI18" t="n">
-        <v>0.02586406644362148</v>
+        <v>-0.0955212851507726</v>
       </c>
       <c r="DJ18" t="n">
-        <v>0.007079006932766817</v>
+        <v>0.05717134555870657</v>
       </c>
       <c r="DK18" t="n">
         <v>-0</v>
@@ -10457,34 +10457,34 @@
         <v>-0</v>
       </c>
       <c r="DO18" t="n">
-        <v>-0.006781662007949998</v>
+        <v>-0.01344923766967236</v>
       </c>
       <c r="DP18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ18" t="n">
         <v>0</v>
       </c>
       <c r="DR18" t="n">
-        <v>0.01788579728714385</v>
+        <v>-0.06585807634744219</v>
       </c>
       <c r="DS18" t="n">
-        <v>-0.008324347205209054</v>
+        <v>0.04062000882953606</v>
       </c>
       <c r="DT18" t="n">
         <v>-0</v>
       </c>
       <c r="DU18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW18" t="n">
         <v>0</v>
       </c>
       <c r="DX18" t="n">
-        <v>-0.04172477594334412</v>
+        <v>0.01409270176827759</v>
       </c>
       <c r="DY18" t="n">
         <v>0</v>
@@ -10493,40 +10493,40 @@
         <v>-0</v>
       </c>
       <c r="EA18" t="n">
-        <v>0.01874645529140154</v>
+        <v>-0.04495200666367587</v>
       </c>
       <c r="EB18" t="n">
-        <v>0.01161392802629558</v>
+        <v>0.02367818620302259</v>
       </c>
       <c r="EC18" t="n">
         <v>-0</v>
       </c>
       <c r="ED18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG18" t="n">
-        <v>-0.03046951967564806</v>
+        <v>-0.0390110693064973</v>
       </c>
       <c r="EH18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI18" t="n">
         <v>-0</v>
       </c>
       <c r="EJ18" t="n">
-        <v>0.007045408054830694</v>
+        <v>0.0195793374590973</v>
       </c>
       <c r="EK18" t="n">
-        <v>0.02425673387379929</v>
+        <v>0.003155725963663686</v>
       </c>
       <c r="EL18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM18" t="n">
         <v>-0</v>
@@ -10535,22 +10535,22 @@
         <v>-0</v>
       </c>
       <c r="EO18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP18" t="n">
-        <v>-0.009827443909543555</v>
+        <v>-0.01233942355497336</v>
       </c>
       <c r="EQ18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES18" t="n">
-        <v>0.006522964190888415</v>
+        <v>0.002364471830275962</v>
       </c>
       <c r="ET18" t="n">
-        <v>0.005877779717316957</v>
+        <v>0.07983689841976564</v>
       </c>
       <c r="EU18" t="n">
         <v>0</v>
@@ -10559,58 +10559,58 @@
         <v>0</v>
       </c>
       <c r="EW18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY18" t="n">
-        <v>-0.02103444219215935</v>
+        <v>-0.07685724802631483</v>
       </c>
       <c r="EZ18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA18" t="n">
         <v>-0</v>
       </c>
       <c r="FB18" t="n">
-        <v>0.01105978135877241</v>
+        <v>-0.005280458213963516</v>
       </c>
       <c r="FC18" t="n">
-        <v>0.02903842041241254</v>
+        <v>0.03741108932936915</v>
       </c>
       <c r="FD18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE18" t="n">
         <v>-0</v>
       </c>
       <c r="FF18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG18" t="n">
         <v>0</v>
       </c>
       <c r="FH18" t="n">
-        <v>-0.02336827631257295</v>
+        <v>0.1320640040835579</v>
       </c>
       <c r="FI18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ18" t="n">
         <v>-0</v>
       </c>
       <c r="FK18" t="n">
-        <v>0.007236959987348461</v>
+        <v>-0.06257672375785009</v>
       </c>
       <c r="FL18" t="n">
-        <v>0.01423656440811494</v>
+        <v>0.09404238662467804</v>
       </c>
       <c r="FM18" t="n">
         <v>0</v>
       </c>
       <c r="FN18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO18" t="n">
         <v>0</v>
@@ -10619,55 +10619,55 @@
         <v>0</v>
       </c>
       <c r="FQ18" t="n">
-        <v>0.005684979372316152</v>
+        <v>0.03684908639976929</v>
       </c>
       <c r="FR18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS18" t="n">
         <v>-0</v>
       </c>
       <c r="FT18" t="n">
-        <v>-0.02068423631315137</v>
+        <v>-0.06688913564655337</v>
       </c>
       <c r="FU18" t="n">
-        <v>0.008726168620858605</v>
+        <v>-0.02252705824033941</v>
       </c>
       <c r="FV18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ18" t="n">
-        <v>-0.0007518997508050961</v>
+        <v>-0.02870145490651067</v>
       </c>
       <c r="GA18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB18" t="n">
         <v>-0</v>
       </c>
       <c r="GC18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD18" t="n">
-        <v>-0.008598198111988859</v>
+        <v>0.05832435713111219</v>
       </c>
       <c r="GE18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -10675,22 +10675,22 @@
         <v>0</v>
       </c>
       <c r="B19" t="n">
-        <v>0.5813243576885919</v>
+        <v>0.2140285096176106</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2206994894259464</v>
+        <v>-0.1620589676380244</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.07252604116140544</v>
+        <v>-0.02155504363874082</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -10702,16 +10702,16 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0.3569896699763817</v>
+        <v>0.2200142189123537</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.2071593044659994</v>
+        <v>-0.1873635397933112</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.06665193226483974</v>
+        <v>-0.05862286185882077</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -10729,133 +10729,133 @@
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1249257747491337</v>
+        <v>0.0419436702193044</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.02355359952968996</v>
+        <v>-0.04274917345693774</v>
       </c>
       <c r="W19" t="n">
-        <v>0.1110585249895825</v>
+        <v>-0.06472007069701625</v>
       </c>
       <c r="X19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
         <v>-0</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA19" t="n">
         <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>0.03518189401378809</v>
+        <v>-0.06367616607114929</v>
       </c>
       <c r="AD19" t="n">
         <v>-0</v>
       </c>
       <c r="AE19" t="n">
-        <v>-0.001077197337505317</v>
+        <v>-0.09847575367799817</v>
       </c>
       <c r="AF19" t="n">
-        <v>-0.01199750620940051</v>
+        <v>-0.06272299148959753</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="n">
         <v>0</v>
       </c>
       <c r="AL19" t="n">
-        <v>0.02150029386535373</v>
+        <v>0.07433204246326182</v>
       </c>
       <c r="AM19" t="n">
         <v>-0</v>
       </c>
       <c r="AN19" t="n">
-        <v>-0.07057779939127096</v>
+        <v>-0.08785537101436791</v>
       </c>
       <c r="AO19" t="n">
-        <v>-0.05701923833431558</v>
+        <v>0.02079676264153217</v>
       </c>
       <c r="AP19" t="n">
         <v>0</v>
       </c>
       <c r="AQ19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS19" t="n">
         <v>0</v>
       </c>
       <c r="AT19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU19" t="n">
-        <v>0.5025124717972149</v>
+        <v>0.2090295542808654</v>
       </c>
       <c r="AV19" t="n">
         <v>-0</v>
       </c>
       <c r="AW19" t="n">
-        <v>0.02190687204463071</v>
+        <v>-0.06907948039734998</v>
       </c>
       <c r="AX19" t="n">
-        <v>0.1062287837388484</v>
+        <v>-0.1349588446713372</v>
       </c>
       <c r="AY19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC19" t="n">
         <v>0</v>
       </c>
       <c r="BD19" t="n">
-        <v>0.05983557086145651</v>
+        <v>-0.006550267135237544</v>
       </c>
       <c r="BE19" t="n">
         <v>0</v>
       </c>
       <c r="BF19" t="n">
-        <v>-0.206401151511279</v>
+        <v>-0.04782362833881886</v>
       </c>
       <c r="BG19" t="n">
-        <v>-0.1324715814607463</v>
+        <v>-0.004683968080500749</v>
       </c>
       <c r="BH19" t="n">
         <v>0</v>
       </c>
       <c r="BI19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK19" t="n">
         <v>0</v>
@@ -10864,16 +10864,16 @@
         <v>-0</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.1583608267954703</v>
+        <v>0.00985824007954289</v>
       </c>
       <c r="BN19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO19" t="n">
-        <v>0.06112346576495088</v>
+        <v>0.04943320495001371</v>
       </c>
       <c r="BP19" t="n">
-        <v>0.1992811513780138</v>
+        <v>0.05537617600038331</v>
       </c>
       <c r="BQ19" t="n">
         <v>-0</v>
@@ -10885,52 +10885,52 @@
         <v>-0</v>
       </c>
       <c r="BT19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU19" t="n">
         <v>0</v>
       </c>
       <c r="BV19" t="n">
-        <v>0.1642993282539399</v>
+        <v>0.100733829253074</v>
       </c>
       <c r="BW19" t="n">
         <v>0</v>
       </c>
       <c r="BX19" t="n">
-        <v>0.00212385463958162</v>
+        <v>-0.07995804066813421</v>
       </c>
       <c r="BY19" t="n">
-        <v>0.05186101998581934</v>
+        <v>-0.01379174993439551</v>
       </c>
       <c r="BZ19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA19" t="n">
         <v>-0</v>
       </c>
       <c r="CB19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD19" t="n">
         <v>-0</v>
       </c>
       <c r="CE19" t="n">
-        <v>-0.1117997928943105</v>
+        <v>-0.05996584714168852</v>
       </c>
       <c r="CF19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG19" t="n">
-        <v>0.004731869409532737</v>
+        <v>0.08514574165648765</v>
       </c>
       <c r="CH19" t="n">
-        <v>-0.01736936817915298</v>
+        <v>0.01058404678934329</v>
       </c>
       <c r="CI19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CJ19" t="n">
         <v>0</v>
@@ -10942,28 +10942,28 @@
         <v>0</v>
       </c>
       <c r="CM19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN19" t="n">
-        <v>-0.01068045688767222</v>
+        <v>-0.04769037141456656</v>
       </c>
       <c r="CO19" t="n">
         <v>-0</v>
       </c>
       <c r="CP19" t="n">
-        <v>-0.1212422279322519</v>
+        <v>0.1385422200882636</v>
       </c>
       <c r="CQ19" t="n">
-        <v>-0.111511230346818</v>
+        <v>0.02258257277255022</v>
       </c>
       <c r="CR19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS19" t="n">
         <v>-0</v>
       </c>
       <c r="CT19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU19" t="n">
         <v>-0</v>
@@ -10972,43 +10972,43 @@
         <v>0</v>
       </c>
       <c r="CW19" t="n">
-        <v>-0.07739655762398902</v>
+        <v>-0.05732712844428756</v>
       </c>
       <c r="CX19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY19" t="n">
-        <v>0.04811590700710487</v>
+        <v>0.08833178482097961</v>
       </c>
       <c r="CZ19" t="n">
-        <v>-0.02580664016101752</v>
+        <v>0.0198981360659001</v>
       </c>
       <c r="DA19" t="n">
         <v>0</v>
       </c>
       <c r="DB19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC19" t="n">
         <v>-0</v>
       </c>
       <c r="DD19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE19" t="n">
         <v>0</v>
       </c>
       <c r="DF19" t="n">
-        <v>-0.04762004907848635</v>
+        <v>-0.04878290384335696</v>
       </c>
       <c r="DG19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH19" t="n">
-        <v>0.06158190868520314</v>
+        <v>0.02118362689974244</v>
       </c>
       <c r="DI19" t="n">
-        <v>0.03325450218359662</v>
+        <v>-0.02851880885602913</v>
       </c>
       <c r="DJ19" t="n">
         <v>-0</v>
@@ -11023,28 +11023,28 @@
         <v>0</v>
       </c>
       <c r="DN19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO19" t="n">
-        <v>-0.08595384562032246</v>
+        <v>-0.03986818059830998</v>
       </c>
       <c r="DP19" t="n">
         <v>0</v>
       </c>
       <c r="DQ19" t="n">
-        <v>0.004288517580598857</v>
+        <v>-0.01274351768998171</v>
       </c>
       <c r="DR19" t="n">
-        <v>-0.04198705855323432</v>
+        <v>-0.008623886766911514</v>
       </c>
       <c r="DS19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT19" t="n">
         <v>-0</v>
       </c>
       <c r="DU19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV19" t="n">
         <v>0</v>
@@ -11053,19 +11053,19 @@
         <v>-0</v>
       </c>
       <c r="DX19" t="n">
-        <v>-0.1167563420244909</v>
+        <v>0.01292444487786096</v>
       </c>
       <c r="DY19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ19" t="n">
-        <v>-0.01496696756663771</v>
+        <v>0.07666161945503448</v>
       </c>
       <c r="EA19" t="n">
-        <v>0.04456813443004735</v>
+        <v>-0.04614350998299566</v>
       </c>
       <c r="EB19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EC19" t="n">
         <v>-0</v>
@@ -11074,85 +11074,85 @@
         <v>0</v>
       </c>
       <c r="EE19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG19" t="n">
-        <v>-0.09548131834028595</v>
+        <v>-0.03981101147317752</v>
       </c>
       <c r="EH19" t="n">
         <v>-0</v>
       </c>
       <c r="EI19" t="n">
-        <v>0.01601281293796111</v>
+        <v>0.06031493344383522</v>
       </c>
       <c r="EJ19" t="n">
-        <v>0.06163472843071433</v>
+        <v>0.0539949693488185</v>
       </c>
       <c r="EK19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP19" t="n">
-        <v>-0.002499175480886409</v>
+        <v>-0.001278404828596262</v>
       </c>
       <c r="EQ19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER19" t="n">
-        <v>-0.008703273729854412</v>
+        <v>0.0536409264515467</v>
       </c>
       <c r="ES19" t="n">
-        <v>0.02338733960352353</v>
+        <v>-0.02447356474861561</v>
       </c>
       <c r="ET19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV19" t="n">
         <v>0</v>
       </c>
       <c r="EW19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX19" t="n">
         <v>-0</v>
       </c>
       <c r="EY19" t="n">
-        <v>-0.07610308434348266</v>
+        <v>-0.06241191557339784</v>
       </c>
       <c r="EZ19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA19" t="n">
-        <v>0.003396274756274597</v>
+        <v>0.1073159268335619</v>
       </c>
       <c r="FB19" t="n">
-        <v>0.009733433973316323</v>
+        <v>-0.001413111506326092</v>
       </c>
       <c r="FC19" t="n">
         <v>-0</v>
       </c>
       <c r="FD19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF19" t="n">
         <v>0</v>
@@ -11161,16 +11161,16 @@
         <v>0</v>
       </c>
       <c r="FH19" t="n">
-        <v>-0.08058879776498599</v>
+        <v>0.09852467641528358</v>
       </c>
       <c r="FI19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ19" t="n">
-        <v>0.00641199004439016</v>
+        <v>0.06408232173334319</v>
       </c>
       <c r="FK19" t="n">
-        <v>0.05149287077661532</v>
+        <v>-0.02704003936808545</v>
       </c>
       <c r="FL19" t="n">
         <v>-0</v>
@@ -11182,28 +11182,28 @@
         <v>-0</v>
       </c>
       <c r="FO19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ19" t="n">
-        <v>-0.05826825703075308</v>
+        <v>0.0413641989796804</v>
       </c>
       <c r="FR19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS19" t="n">
-        <v>0.01198161159234575</v>
+        <v>0.1080327000434127</v>
       </c>
       <c r="FT19" t="n">
-        <v>-0.08264678248169126</v>
+        <v>-0.04951974498167596</v>
       </c>
       <c r="FU19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW19" t="n">
         <v>-0</v>
@@ -11212,28 +11212,28 @@
         <v>0</v>
       </c>
       <c r="FY19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ19" t="n">
-        <v>0.07896142475276292</v>
+        <v>-0.009315359319941627</v>
       </c>
       <c r="GA19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB19" t="n">
-        <v>-0.132879181348353</v>
+        <v>0.02432941102280659</v>
       </c>
       <c r="GC19" t="n">
         <v>-0</v>
       </c>
       <c r="GD19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG19" t="n">
         <v>-0</v>
@@ -11244,7 +11244,7 @@
         <v>-0</v>
       </c>
       <c r="B20" t="n">
-        <v>-0.9555535467151666</v>
+        <v>-0.3533002079028263</v>
       </c>
       <c r="C20" t="n">
         <v>-0</v>
@@ -11253,13 +11253,13 @@
         <v>-0</v>
       </c>
       <c r="E20" t="n">
-        <v>0.125218400974022</v>
+        <v>0.1283585112200805</v>
       </c>
       <c r="F20" t="n">
-        <v>1.367357707842619</v>
+        <v>0.5584751156981523</v>
       </c>
       <c r="G20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -11268,10 +11268,10 @@
         <v>-0</v>
       </c>
       <c r="J20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.774964630484031</v>
+        <v>-0.541171906617035</v>
       </c>
       <c r="L20" t="n">
         <v>-0</v>
@@ -11280,10 +11280,10 @@
         <v>-0</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.08593641735988644</v>
+        <v>0.1752026624678895</v>
       </c>
       <c r="O20" t="n">
-        <v>0.9513003471920908</v>
+        <v>0.5923779444512263</v>
       </c>
       <c r="P20" t="n">
         <v>-0</v>
@@ -11292,52 +11292,52 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.08767046504047085</v>
+        <v>-0.1037396363313098</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V20" t="n">
         <v>-0</v>
       </c>
       <c r="W20" t="n">
-        <v>0.255751955271979</v>
+        <v>0.1335945490888242</v>
       </c>
       <c r="X20" t="n">
-        <v>0.1525096043649294</v>
+        <v>0.09325074991965922</v>
       </c>
       <c r="Y20" t="n">
         <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
         <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>-0.0365806195114871</v>
+        <v>0.01487611978664904</v>
       </c>
       <c r="AD20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
         <v>-0</v>
       </c>
       <c r="AF20" t="n">
-        <v>0.193784556180716</v>
+        <v>0.1787230598845983</v>
       </c>
       <c r="AG20" t="n">
-        <v>0.136856267870123</v>
+        <v>-0.03626830346152047</v>
       </c>
       <c r="AH20" t="n">
         <v>-0</v>
@@ -11346,13 +11346,13 @@
         <v>0</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK20" t="n">
         <v>-0</v>
       </c>
       <c r="AL20" t="n">
-        <v>-0.106279521899657</v>
+        <v>-0.06010904197959577</v>
       </c>
       <c r="AM20" t="n">
         <v>0</v>
@@ -11361,13 +11361,13 @@
         <v>-0</v>
       </c>
       <c r="AO20" t="n">
-        <v>-0.04253660065987656</v>
+        <v>0.02677046183071049</v>
       </c>
       <c r="AP20" t="n">
-        <v>0.2565428489980843</v>
+        <v>0.08494498845276764</v>
       </c>
       <c r="AQ20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR20" t="n">
         <v>0</v>
@@ -11376,37 +11376,37 @@
         <v>-0</v>
       </c>
       <c r="AT20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU20" t="n">
-        <v>-0.6172717534061476</v>
+        <v>-0.6818937221120029</v>
       </c>
       <c r="AV20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW20" t="n">
         <v>-0</v>
       </c>
       <c r="AX20" t="n">
-        <v>0.2705298344331309</v>
+        <v>0.08214408961948282</v>
       </c>
       <c r="AY20" t="n">
-        <v>0.8951261879568482</v>
+        <v>0.3424625867890921</v>
       </c>
       <c r="AZ20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA20" t="n">
         <v>0</v>
       </c>
       <c r="BB20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD20" t="n">
-        <v>-0.2789822097179999</v>
+        <v>0.1842094098689358</v>
       </c>
       <c r="BE20" t="n">
         <v>-0</v>
@@ -11415,10 +11415,10 @@
         <v>-0</v>
       </c>
       <c r="BG20" t="n">
-        <v>0.1325191045465678</v>
+        <v>0.1129157665574255</v>
       </c>
       <c r="BH20" t="n">
-        <v>0.341250828619303</v>
+        <v>0.03919596040593061</v>
       </c>
       <c r="BI20" t="n">
         <v>-0</v>
@@ -11427,52 +11427,52 @@
         <v>0</v>
       </c>
       <c r="BK20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BL20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BM20" t="n">
-        <v>-0.3118136950174849</v>
+        <v>-0.1794629255678651</v>
       </c>
       <c r="BN20" t="n">
         <v>0</v>
       </c>
       <c r="BO20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP20" t="n">
-        <v>-0.1115819091716627</v>
+        <v>-0.1475984104975039</v>
       </c>
       <c r="BQ20" t="n">
-        <v>0.02734112332789938</v>
+        <v>-0.1335762630905444</v>
       </c>
       <c r="BR20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BS20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT20" t="n">
         <v>-0</v>
       </c>
       <c r="BU20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV20" t="n">
-        <v>-0.3985786115602167</v>
+        <v>-0.3068061675727154</v>
       </c>
       <c r="BW20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX20" t="n">
         <v>-0</v>
       </c>
       <c r="BY20" t="n">
-        <v>0.08213475946453966</v>
+        <v>0.007568137216141973</v>
       </c>
       <c r="BZ20" t="n">
-        <v>0.3854074217352527</v>
+        <v>0.2026751854423259</v>
       </c>
       <c r="CA20" t="n">
         <v>0</v>
@@ -11487,22 +11487,22 @@
         <v>0</v>
       </c>
       <c r="CE20" t="n">
-        <v>0.1664524391208402</v>
+        <v>0.1047180473073995</v>
       </c>
       <c r="CF20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CG20" t="n">
         <v>0</v>
       </c>
       <c r="CH20" t="n">
-        <v>-0.02167547117803665</v>
+        <v>-0.06922820647789719</v>
       </c>
       <c r="CI20" t="n">
-        <v>-0.2299443871168447</v>
+        <v>-0.147455566111848</v>
       </c>
       <c r="CJ20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK20" t="n">
         <v>-0</v>
@@ -11514,7 +11514,7 @@
         <v>-0</v>
       </c>
       <c r="CN20" t="n">
-        <v>0.04461671217303093</v>
+        <v>0.1984712269322874</v>
       </c>
       <c r="CO20" t="n">
         <v>0</v>
@@ -11523,16 +11523,16 @@
         <v>0</v>
       </c>
       <c r="CQ20" t="n">
-        <v>-0.228126154058156</v>
+        <v>-0.03158455191819531</v>
       </c>
       <c r="CR20" t="n">
-        <v>0.02552499353990513</v>
+        <v>0.007798438236878267</v>
       </c>
       <c r="CS20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU20" t="n">
         <v>0</v>
@@ -11541,22 +11541,22 @@
         <v>0</v>
       </c>
       <c r="CW20" t="n">
-        <v>0.1385072600200643</v>
+        <v>0.09824052826777047</v>
       </c>
       <c r="CX20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CY20" t="n">
         <v>-0</v>
       </c>
       <c r="CZ20" t="n">
-        <v>-0.02132292414102758</v>
+        <v>-0.06746262848456921</v>
       </c>
       <c r="DA20" t="n">
-        <v>-0.2484861342905257</v>
+        <v>-0.1692339418255203</v>
       </c>
       <c r="DB20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC20" t="n">
         <v>0</v>
@@ -11565,49 +11565,49 @@
         <v>-0</v>
       </c>
       <c r="DE20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF20" t="n">
-        <v>0.2395404847638643</v>
+        <v>0.1115678090768223</v>
       </c>
       <c r="DG20" t="n">
         <v>0</v>
       </c>
       <c r="DH20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DI20" t="n">
-        <v>-0.2939200123485097</v>
+        <v>0.1141473448940579</v>
       </c>
       <c r="DJ20" t="n">
-        <v>0.003028341296505732</v>
+        <v>-0.01179284602614442</v>
       </c>
       <c r="DK20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL20" t="n">
         <v>-0</v>
       </c>
       <c r="DM20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN20" t="n">
         <v>0</v>
       </c>
       <c r="DO20" t="n">
-        <v>0.0383313838986394</v>
+        <v>-0.01895351364657017</v>
       </c>
       <c r="DP20" t="n">
         <v>-0</v>
       </c>
       <c r="DQ20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DR20" t="n">
-        <v>-0.05398197819079133</v>
+        <v>0.05685659910989263</v>
       </c>
       <c r="DS20" t="n">
-        <v>-0.1432666533808165</v>
+        <v>-0.1433323187563683</v>
       </c>
       <c r="DT20" t="n">
         <v>0</v>
@@ -11616,25 +11616,25 @@
         <v>0</v>
       </c>
       <c r="DV20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DX20" t="n">
-        <v>0.1286753574867674</v>
+        <v>0.1170513750861301</v>
       </c>
       <c r="DY20" t="n">
         <v>0</v>
       </c>
       <c r="DZ20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EA20" t="n">
-        <v>-0.1064783166537736</v>
+        <v>0.01348738087853794</v>
       </c>
       <c r="EB20" t="n">
-        <v>-0.1019188304297612</v>
+        <v>-0.01317884500368069</v>
       </c>
       <c r="EC20" t="n">
         <v>0</v>
@@ -11643,31 +11643,31 @@
         <v>-0</v>
       </c>
       <c r="EE20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EF20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG20" t="n">
-        <v>0.1043654927206298</v>
+        <v>0.04332721976141553</v>
       </c>
       <c r="EH20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ20" t="n">
-        <v>-0.05874249858191107</v>
+        <v>-0.03134420921569546</v>
       </c>
       <c r="EK20" t="n">
-        <v>-0.1857520990892341</v>
+        <v>-0.06111526526512318</v>
       </c>
       <c r="EL20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EM20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN20" t="n">
         <v>0</v>
@@ -11676,7 +11676,7 @@
         <v>-0</v>
       </c>
       <c r="EP20" t="n">
-        <v>0.09569497589024525</v>
+        <v>0.04958670946011468</v>
       </c>
       <c r="EQ20" t="n">
         <v>0</v>
@@ -11685,25 +11685,25 @@
         <v>-0</v>
       </c>
       <c r="ES20" t="n">
-        <v>-0.008703144792652799</v>
+        <v>-0.05905340457962627</v>
       </c>
       <c r="ET20" t="n">
-        <v>0.002452998929811908</v>
+        <v>0.147769981378384</v>
       </c>
       <c r="EU20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV20" t="n">
         <v>-0</v>
       </c>
       <c r="EW20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX20" t="n">
         <v>-0</v>
       </c>
       <c r="EY20" t="n">
-        <v>0.1321316036627264</v>
+        <v>0.121034147440436</v>
       </c>
       <c r="EZ20" t="n">
         <v>0</v>
@@ -11712,13 +11712,13 @@
         <v>0</v>
       </c>
       <c r="FB20" t="n">
-        <v>-0.0492038552903505</v>
+        <v>-0.02740460909330773</v>
       </c>
       <c r="FC20" t="n">
-        <v>-0.2257031928486266</v>
+        <v>-0.1478208679297496</v>
       </c>
       <c r="FD20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE20" t="n">
         <v>-0</v>
@@ -11730,7 +11730,7 @@
         <v>-0</v>
       </c>
       <c r="FH20" t="n">
-        <v>-0.0147379497163268</v>
+        <v>-0.083775260201131</v>
       </c>
       <c r="FI20" t="n">
         <v>-0</v>
@@ -11739,10 +11739,10 @@
         <v>0</v>
       </c>
       <c r="FK20" t="n">
-        <v>-0.0152848375093764</v>
+        <v>0.06975006930206748</v>
       </c>
       <c r="FL20" t="n">
-        <v>-0.1619539842595783</v>
+        <v>-0.08667578970839165</v>
       </c>
       <c r="FM20" t="n">
         <v>-0</v>
@@ -11751,52 +11751,52 @@
         <v>0</v>
       </c>
       <c r="FO20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FQ20" t="n">
-        <v>-0.01578419601728682</v>
+        <v>0.03449667826520292</v>
       </c>
       <c r="FR20" t="n">
         <v>0</v>
       </c>
       <c r="FS20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FT20" t="n">
-        <v>0.1171188790328716</v>
+        <v>0.1502937213230972</v>
       </c>
       <c r="FU20" t="n">
-        <v>-0.1960341491796673</v>
+        <v>0.1790597287533324</v>
       </c>
       <c r="FV20" t="n">
         <v>0</v>
       </c>
       <c r="FW20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX20" t="n">
         <v>-0</v>
       </c>
       <c r="FY20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FZ20" t="n">
-        <v>-0.03153613549508923</v>
+        <v>0.04596655001965494</v>
       </c>
       <c r="GA20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB20" t="n">
         <v>0</v>
       </c>
       <c r="GC20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD20" t="n">
-        <v>0.1265500728807336</v>
+        <v>-0.07512856400080017</v>
       </c>
       <c r="GE20" t="n">
         <v>0</v>
@@ -11805,12 +11805,12 @@
         <v>-0</v>
       </c>
       <c r="GG20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>0.1579309657606398</v>
+        <v>0.3395026015448797</v>
       </c>
       <c r="B21" t="n">
         <v>-0</v>
@@ -11822,13 +11822,13 @@
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.002062509904998334</v>
+        <v>5.031951349659168e-05</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.1440615630925162</v>
+        <v>-0.1375987411705322</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H21" t="n">
         <v>-0</v>
@@ -11837,10 +11837,10 @@
         <v>-0</v>
       </c>
       <c r="J21" t="n">
-        <v>0.1233197493734981</v>
+        <v>0.3116027338226297</v>
       </c>
       <c r="K21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -11849,40 +11849,40 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>0.01531587392365156</v>
+        <v>-0.150273118281725</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.1081050802752104</v>
+        <v>-0.2051877834276671</v>
       </c>
       <c r="P21" t="n">
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
         <v>-0</v>
       </c>
       <c r="S21" t="n">
-        <v>0.02037933682254647</v>
+        <v>-0.03456355767217349</v>
       </c>
       <c r="T21" t="n">
         <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.01996452474508568</v>
+        <v>0.03227011457483955</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.04084137734115367</v>
+        <v>-0.02549758402511463</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z21" t="n">
         <v>0</v>
@@ -11891,7 +11891,7 @@
         <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.02430063161776922</v>
+        <v>0.02669716617710559</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -11900,16 +11900,16 @@
         <v>-0</v>
       </c>
       <c r="AE21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>-0.01015817872023107</v>
+        <v>-0.05909778891144793</v>
       </c>
       <c r="AG21" t="n">
-        <v>-0.01878738735423515</v>
+        <v>0.09647983708093698</v>
       </c>
       <c r="AH21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -11918,49 +11918,49 @@
         <v>-0</v>
       </c>
       <c r="AK21" t="n">
-        <v>0.02660686185573689</v>
+        <v>0.0412893496044962</v>
       </c>
       <c r="AL21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AM21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO21" t="n">
-        <v>0.02169268939640987</v>
+        <v>0.0375131562887402</v>
       </c>
       <c r="AP21" t="n">
-        <v>-0.01854946827056193</v>
+        <v>0.02135514439549495</v>
       </c>
       <c r="AQ21" t="n">
         <v>0</v>
       </c>
       <c r="AR21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS21" t="n">
         <v>0</v>
       </c>
       <c r="AT21" t="n">
-        <v>0.08048047464782969</v>
+        <v>0.1256104307242744</v>
       </c>
       <c r="AU21" t="n">
         <v>-0</v>
       </c>
       <c r="AV21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW21" t="n">
         <v>0</v>
       </c>
       <c r="AX21" t="n">
-        <v>-0.04839249995448342</v>
+        <v>-0.005310389798564583</v>
       </c>
       <c r="AY21" t="n">
-        <v>-0.06952785216480141</v>
+        <v>-0.1122869878121553</v>
       </c>
       <c r="AZ21" t="n">
         <v>0</v>
@@ -11972,22 +11972,22 @@
         <v>0</v>
       </c>
       <c r="BC21" t="n">
-        <v>0.03912543410912706</v>
+        <v>0.1127501272889474</v>
       </c>
       <c r="BD21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BE21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF21" t="n">
         <v>0</v>
       </c>
       <c r="BG21" t="n">
-        <v>0.01978195399292558</v>
+        <v>-0.02715267139134464</v>
       </c>
       <c r="BH21" t="n">
-        <v>-0.06206423708270363</v>
+        <v>0.07047526441116896</v>
       </c>
       <c r="BI21" t="n">
         <v>0</v>
@@ -11999,52 +11999,52 @@
         <v>-0</v>
       </c>
       <c r="BL21" t="n">
-        <v>-0.0009339359621069522</v>
+        <v>-0.05993342263963333</v>
       </c>
       <c r="BM21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BN21" t="n">
         <v>-0</v>
       </c>
       <c r="BO21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP21" t="n">
-        <v>-0.02317516172825269</v>
+        <v>-0.154309370633205</v>
       </c>
       <c r="BQ21" t="n">
-        <v>0.005510130071806345</v>
+        <v>0.04613003827270573</v>
       </c>
       <c r="BR21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS21" t="n">
         <v>0</v>
       </c>
       <c r="BT21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BU21" t="n">
-        <v>0.04272999750064014</v>
+        <v>0.05848808710617623</v>
       </c>
       <c r="BV21" t="n">
         <v>0</v>
       </c>
       <c r="BW21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BX21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY21" t="n">
-        <v>-0.009650314691324205</v>
+        <v>-0.09802971521207755</v>
       </c>
       <c r="BZ21" t="n">
-        <v>-0.04152762580788315</v>
+        <v>-0.05682214246312278</v>
       </c>
       <c r="CA21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB21" t="n">
         <v>0</v>
@@ -12053,25 +12053,25 @@
         <v>0</v>
       </c>
       <c r="CD21" t="n">
-        <v>-0.02950793266379362</v>
+        <v>-0.07974596159020114</v>
       </c>
       <c r="CE21" t="n">
         <v>0</v>
       </c>
       <c r="CF21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CH21" t="n">
-        <v>0.003119697467546191</v>
+        <v>0.0357180108896093</v>
       </c>
       <c r="CI21" t="n">
-        <v>0.03210219308404522</v>
+        <v>0.04092891997628759</v>
       </c>
       <c r="CJ21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK21" t="n">
         <v>0</v>
@@ -12080,34 +12080,34 @@
         <v>0</v>
       </c>
       <c r="CM21" t="n">
-        <v>-0.003887501391928498</v>
+        <v>-0.02830392360850174</v>
       </c>
       <c r="CN21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CO21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ21" t="n">
-        <v>0.03765491202443046</v>
+        <v>0.2036461302788827</v>
       </c>
       <c r="CR21" t="n">
-        <v>0.006480832166932005</v>
+        <v>-0.09116718205522145</v>
       </c>
       <c r="CS21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT21" t="n">
         <v>-0</v>
       </c>
       <c r="CU21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CV21" t="n">
-        <v>-0.02748902616889345</v>
+        <v>-0.08828320624860436</v>
       </c>
       <c r="CW21" t="n">
         <v>-0</v>
@@ -12119,64 +12119,64 @@
         <v>-0</v>
       </c>
       <c r="CZ21" t="n">
-        <v>0.006438022574553357</v>
+        <v>0.03822012176900542</v>
       </c>
       <c r="DA21" t="n">
-        <v>0.02715361035583444</v>
+        <v>0.05532172916999099</v>
       </c>
       <c r="DB21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC21" t="n">
         <v>-0</v>
       </c>
       <c r="DD21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE21" t="n">
-        <v>-0.0003229328054935052</v>
+        <v>-0.002293309109758107</v>
       </c>
       <c r="DF21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DG21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI21" t="n">
-        <v>0.003639453667989901</v>
+        <v>-0.01222602261182273</v>
       </c>
       <c r="DJ21" t="n">
-        <v>0.02504617243515229</v>
+        <v>0.02021265861381678</v>
       </c>
       <c r="DK21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL21" t="n">
         <v>0</v>
       </c>
       <c r="DM21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN21" t="n">
-        <v>-0.01165685776789508</v>
+        <v>-0.03832120989353538</v>
       </c>
       <c r="DO21" t="n">
         <v>0</v>
       </c>
       <c r="DP21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DQ21" t="n">
         <v>0</v>
       </c>
       <c r="DR21" t="n">
-        <v>0.005441236865295638</v>
+        <v>-0.008711802460212317</v>
       </c>
       <c r="DS21" t="n">
-        <v>0.0332996145674316</v>
+        <v>0.07290878640664013</v>
       </c>
       <c r="DT21" t="n">
         <v>-0</v>
@@ -12185,13 +12185,13 @@
         <v>0</v>
       </c>
       <c r="DV21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW21" t="n">
-        <v>-0.009573496140179692</v>
+        <v>-0.0007401236901088175</v>
       </c>
       <c r="DX21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DY21" t="n">
         <v>-0</v>
@@ -12200,37 +12200,37 @@
         <v>0</v>
       </c>
       <c r="EA21" t="n">
-        <v>0.006375622279817778</v>
+        <v>0.2134900589116847</v>
       </c>
       <c r="EB21" t="n">
-        <v>0.01023388080882538</v>
+        <v>0.04103592815788894</v>
       </c>
       <c r="EC21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED21" t="n">
         <v>-0</v>
       </c>
       <c r="EE21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF21" t="n">
-        <v>-0.02497385562171606</v>
+        <v>-0.003985438414683904</v>
       </c>
       <c r="EG21" t="n">
         <v>0</v>
       </c>
       <c r="EH21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI21" t="n">
         <v>0</v>
       </c>
       <c r="EJ21" t="n">
-        <v>0.01184644214678479</v>
+        <v>-0.01278295147820323</v>
       </c>
       <c r="EK21" t="n">
-        <v>0.01918113999791521</v>
+        <v>0.05479012062848418</v>
       </c>
       <c r="EL21" t="n">
         <v>-0</v>
@@ -12239,10 +12239,10 @@
         <v>0</v>
       </c>
       <c r="EN21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO21" t="n">
-        <v>0.008675408975855503</v>
+        <v>0.06427839405037968</v>
       </c>
       <c r="EP21" t="n">
         <v>0</v>
@@ -12251,13 +12251,13 @@
         <v>-0</v>
       </c>
       <c r="ER21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES21" t="n">
-        <v>-0.01691449656249501</v>
+        <v>0.04933995629361376</v>
       </c>
       <c r="ET21" t="n">
-        <v>0.004402519263486972</v>
+        <v>0.01532645209140761</v>
       </c>
       <c r="EU21" t="n">
         <v>0</v>
@@ -12266,10 +12266,10 @@
         <v>0</v>
       </c>
       <c r="EW21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX21" t="n">
-        <v>-0.02585173574717364</v>
+        <v>-0.07920273255707154</v>
       </c>
       <c r="EY21" t="n">
         <v>0</v>
@@ -12281,13 +12281,13 @@
         <v>0</v>
       </c>
       <c r="FB21" t="n">
-        <v>0.01051616013090552</v>
+        <v>0.03974485033865238</v>
       </c>
       <c r="FC21" t="n">
-        <v>0.02741666215149489</v>
+        <v>0.05466035745958849</v>
       </c>
       <c r="FD21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE21" t="n">
         <v>0</v>
@@ -12296,7 +12296,7 @@
         <v>0</v>
       </c>
       <c r="FG21" t="n">
-        <v>-0.01411831644716053</v>
+        <v>-0.09904359305157003</v>
       </c>
       <c r="FH21" t="n">
         <v>-0</v>
@@ -12308,55 +12308,55 @@
         <v>-0</v>
       </c>
       <c r="FK21" t="n">
-        <v>0.001086091336808162</v>
+        <v>0.0004306745533487138</v>
       </c>
       <c r="FL21" t="n">
-        <v>-0.0007414155784733195</v>
+        <v>0.01996063254442207</v>
       </c>
       <c r="FM21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FP21" t="n">
-        <v>-0.01406957366843699</v>
+        <v>-0.1517896920271032</v>
       </c>
       <c r="FQ21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FR21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FT21" t="n">
-        <v>-0.005908819036342376</v>
+        <v>0.007813253424440746</v>
       </c>
       <c r="FU21" t="n">
-        <v>0.03298655549764764</v>
+        <v>0.1436246770624217</v>
       </c>
       <c r="FV21" t="n">
         <v>-0</v>
       </c>
       <c r="FW21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY21" t="n">
-        <v>0.002011294494542216</v>
+        <v>0.02881906034122671</v>
       </c>
       <c r="FZ21" t="n">
         <v>-0</v>
       </c>
       <c r="GA21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB21" t="n">
         <v>-0</v>
@@ -12365,13 +12365,13 @@
         <v>-0</v>
       </c>
       <c r="GD21" t="n">
-        <v>0.006441024939235725</v>
+        <v>0.03089850698238748</v>
       </c>
       <c r="GE21" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG21" t="n">
         <v>0</v>
